--- a/stories/arbres/TREE-COL-026.xlsx
+++ b/stories/arbres/TREE-COL-026.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau arrive en classe avec maman. Il lève la main. Il faut attendre. Puis il pourra parler.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le tapis, la table, ou la fenêtre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le tapis, Marceau lève la main. Il attend. Puis il parle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le tapis, que fait Marceau d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau a attendu. Puis il a parlé.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2221,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2388,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau attend. Puis il parle.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2581,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2750,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à le tapis, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2917,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3084,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à le tapis, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3251,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3418,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à le tapis, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3585,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3752,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau attend. Puis il parle.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3945,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4114,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à le tapis, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4281,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4448,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à le tapis, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4615,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4782,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à le tapis, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4949,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5116,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau attend. Puis il parle.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5309,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5478,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à le tapis, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5645,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5812,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à le tapis, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5979,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6146,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à le tapis, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6313,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6313,6 +6480,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, Marceau lève la main. Il attend. Puis il parle.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6661,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, que fait Marceau d'abord ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6834,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Attendre, puis parler.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7025,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7192,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau attend. Puis il parle.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7193,6 +7385,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7357,6 +7554,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la table, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7721,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7888,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la table, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8055,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8222,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la table, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8389,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8556,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau attend. Puis il parle.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8749,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8918,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la table, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9085,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9252,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la table, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9419,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9586,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la table, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9753,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9920,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau attend. Puis il parle.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10113,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10282,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la table, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10449,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10616,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la table, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10783,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10950,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la table, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11117,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10977,6 +11284,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la fenêtre, Marceau lève la main. Il attend. Puis il parle.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11465,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la fenêtre, que fait Marceau d'abord ?</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11638,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau a levé la main. Il a attendu. Puis il a parlé.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11829,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11996,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau attend. Puis il parle.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12189,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12358,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la fenêtre, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12525,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12692,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la fenêtre, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12859,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13026,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la fenêtre, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13193,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13360,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau attend. Puis il parle.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13553,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13722,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la fenêtre, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13889,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14056,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la fenêtre, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14223,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14390,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la fenêtre, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14557,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14724,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau attend. Puis il parle.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14917,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15086,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la fenêtre, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15253,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15420,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la fenêtre, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15587,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15754,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la fenêtre, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15921,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16017,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-026.xlsx
+++ b/stories/arbres/TREE-COL-026.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Marceau arrive en classe avec maman. Il lève la main. Il faut attendre. Puis il pourra parler.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le tapis, la table, ou la fenêtre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Sur le tapis, Marceau lève la main. Il attend. Puis il parle.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|Sur le tapis, que fait Marceau d'abord ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Marceau a attendu. Puis il a parlé.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2236,7 @@
           <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2393,6 +2404,7 @@
           <t>narrateur|Marceau attend. Puis il parle.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2600,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2755,6 +2768,7 @@
           <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à le tapis, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2922,6 +2936,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3089,6 +3104,7 @@
           <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à le tapis, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3256,6 +3272,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3423,6 +3440,7 @@
           <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à le tapis, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3590,6 +3608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3757,6 +3776,7 @@
           <t>narrateur|Marceau attend. Puis il parle.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3952,6 +3972,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4119,6 +4140,7 @@
           <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à le tapis, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4286,6 +4308,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4453,6 +4476,7 @@
           <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à le tapis, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4620,6 +4644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4787,6 +4812,7 @@
           <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à le tapis, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4954,6 +4980,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5121,6 +5148,7 @@
           <t>narrateur|Marceau attend. Puis il parle.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5316,6 +5344,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5483,6 +5512,7 @@
           <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à le tapis, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5650,6 +5680,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5817,6 +5848,7 @@
           <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à le tapis, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5984,6 +6016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6151,6 +6184,7 @@
           <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à le tapis, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6318,6 +6352,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6485,6 +6520,7 @@
           <t>narrateur|À la table, Marceau lève la main. Il attend. Puis il parle.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6668,6 +6704,7 @@
           <t>narrateur|À la table, que fait Marceau d'abord ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6839,6 +6876,7 @@
           <t>narrateur|Oui. Attendre, puis parler.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7030,6 +7068,7 @@
           <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7197,6 +7236,7 @@
           <t>narrateur|Marceau attend. Puis il parle.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7392,6 +7432,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7559,6 +7600,7 @@
           <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la table, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7726,6 +7768,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7893,6 +7936,7 @@
           <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la table, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8060,6 +8104,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8227,6 +8272,7 @@
           <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la table, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8394,6 +8440,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8561,6 +8608,7 @@
           <t>narrateur|Marceau attend. Puis il parle.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8756,6 +8804,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8923,6 +8972,7 @@
           <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la table, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9090,6 +9140,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9257,6 +9308,7 @@
           <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la table, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9424,6 +9476,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9591,6 +9644,7 @@
           <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la table, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9758,6 +9812,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9925,6 +9980,7 @@
           <t>narrateur|Marceau attend. Puis il parle.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10120,6 +10176,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10287,6 +10344,7 @@
           <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la table, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10454,6 +10512,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10621,6 +10680,7 @@
           <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la table, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10788,6 +10848,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10955,6 +11016,7 @@
           <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la table, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11122,6 +11184,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11289,6 +11352,7 @@
           <t>narrateur|Près de la fenêtre, Marceau lève la main. Il attend. Puis il parle.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11472,6 +11536,7 @@
           <t>narrateur|Près de la fenêtre, que fait Marceau d'abord ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11643,6 +11708,7 @@
           <t>narrateur|Marceau a levé la main. Il a attendu. Puis il a parlé.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11834,6 +11900,7 @@
           <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12001,6 +12068,7 @@
           <t>narrateur|Marceau attend. Puis il parle.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12196,6 +12264,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12363,6 +12432,7 @@
           <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la fenêtre, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12530,6 +12600,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12697,6 +12768,7 @@
           <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la fenêtre, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12864,6 +12936,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13031,6 +13104,7 @@
           <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la fenêtre, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13198,6 +13272,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13365,6 +13440,7 @@
           <t>narrateur|Marceau attend. Puis il parle.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13560,6 +13636,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13727,6 +13804,7 @@
           <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la fenêtre, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13894,6 +13972,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14061,6 +14140,7 @@
           <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la fenêtre, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14228,6 +14308,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14395,6 +14476,7 @@
           <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la fenêtre, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14562,6 +14644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14729,6 +14812,7 @@
           <t>narrateur|Marceau attend. Puis il parle.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14924,6 +15008,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15091,6 +15176,7 @@
           <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la fenêtre, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15258,6 +15344,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15425,6 +15512,7 @@
           <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la fenêtre, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15592,6 +15680,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15759,6 +15848,7 @@
           <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la fenêtre, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15926,6 +16016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15944,7 +16035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16024,6 +16115,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16038,7 +16143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16225,6 +16330,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-026.xlsx
+++ b/stories/arbres/TREE-COL-026.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marceau attend puis parle</t>
+          <t>L'ardoise et la main d'Aniss</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sur l'ardoise, Aniss a une idée. Il lève la main, il attend, puis il parle, au coin école, avec papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Marceau arrive en classe avec maman. Il lève la main. Il faut attendre. Puis il pourra parler.</t>
+          <t>Le manteau d'Aniss pend au dossier, encore un peu humide. Une craie blanche attend sur l'ardoise. Elle laisse une poussière, toute fine. Dehors, la pluie dessine des ronds sur la vitre. La vitre est embuée, tout bas. Papa pose trois coussins sur le tapis. Le tapis est gris, un peu rêche. Maman ouvre le volet, tout doux. Un rectangle de lumière tombe sur la table. Aniss, on fait l'école, ici ? Oui. On s'assoit. On attend. Puis on parle. En ce moment, Aniss a une idée. Il se tient près de l'ardoise. La craie est froide dans sa main. Papa parle déjà, tout calme. J'ai une idée. Tu lèves la main. Tu attends. Puis tu parles. Aniss lève la main. Il attend. Une goutte glisse encore, sur la vitre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,38 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Marceau arrive en classe avec maman. Il lève la main. Il faut attendre. Puis il pourra parler.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le manteau d'Aniss pend au dossier, encore un peu humide.
+narrateur|Une craie blanche attend sur l'ardoise.
+narrateur|Elle laisse une poussière, toute fine.
+narrateur|Dehors, la pluie dessine des ronds sur la vitre.
+narrateur|La vitre est embuée, tout bas.
+narrateur|Papa pose trois coussins sur le tapis.
+narrateur|Le tapis est gris, un peu rêche.
+narrateur|Maman ouvre le volet, tout doux.
+narrateur|Un rectangle de lumière tombe sur la table.
+maman|Aniss, on fait l'école, ici ?
+enfant-m|Oui.
+papa|On s'assoit.
+papa|On attend.
+papa|Puis on parle.
+narrateur|En ce moment, Aniss a une idée.
+narrateur|Il se tient près de l'ardoise.
+narrateur|La craie est froide dans sa main.
+narrateur|Papa parle déjà, tout calme.
+enfant-m|J'ai une idée.
+maman|Tu lèves la main.
+maman|Tu attends.
+maman|Puis tu parles.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+narrateur|Une goutte glisse encore, sur la vitre.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pluie,craie</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1393,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le tapis, la table, ou la fenêtre.</t>
+          <t>Le coin école a trois places. Le tapis, la table, ou la fenêtre ? On s'assoit. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1557,11 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le tapis, la table, ou la fenêtre.</t>
+          <t>narrateur|Le coin école a trois places.
+papa|Le tapis, la table, ou la fenêtre ?
+maman|On s'assoit.
+maman|On attend.
+maman|Puis on parle.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sur le tapis, Marceau lève la main. Il attend. Puis il parle.</t>
+          <t>Aniss s'assoit sur le tapis gris. Le tapis est un peu rêche, tout chaud. Un fil dépasse, tout doux. Papa pose un coussin, tout près. Moi, je raconte le tapis. Papa parle jusqu'au bout. Aniss a une idée. Il lève la main. Il attend. C'est mon tour ? Oui. C'est ton tour. On a attendu. Puis on parle. Aniss parle, tout doucement. Le tapis chatouille un peu. Bravo, Aniss. Tu as levé la main. Tu as attendu. Puis tu as parlé. Le fil doux reste sous le genou. On peut lever la main, encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,7 +1729,28 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sur le tapis, Marceau lève la main. Il attend. Puis il parle.</t>
+          <t>narrateur|Aniss s'assoit sur le tapis gris.
+narrateur|Le tapis est un peu rêche, tout chaud.
+narrateur|Un fil dépasse, tout doux.
+narrateur|Papa pose un coussin, tout près.
+papa|Moi, je raconte le tapis.
+narrateur|Papa parle jusqu'au bout.
+narrateur|Aniss a une idée.
+narrateur|Il lève la main.
+narrateur|Il attend.
+enfant-m|C'est mon tour ?
+papa|Oui.
+papa|C'est ton tour.
+papa|On a attendu.
+papa|Puis on parle.
+narrateur|Aniss parle, tout doucement.
+enfant-m|Le tapis chatouille un peu.
+maman|Bravo, Aniss.
+maman|Tu as levé la main.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Le fil doux reste sous le genou.
+papa|On peut lever la main, encore.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1713,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sur le tapis, que fait Marceau d'abord ?</t>
+          <t>Sur le tapis, Aniss veut parler. Il fait quoi d'abord ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1869,7 +1934,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sur le tapis, que fait Marceau d'abord ?</t>
+          <t>narrateur|Sur le tapis, Aniss veut parler.
+papa|Il fait quoi d'abord ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1897,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Marceau a attendu. Puis il a parlé.</t>
+          <t>Oui. On attend. Puis on parle. Aniss souffle un peu. Sa main redescend, tout doux. Le tapis reste chaud sous les genoux. J'ai attendu. Bravo. Tu as levé la main. C'est du bon travail, Aniss. Le fil doux chatouille encore. Tu as parlé, après avoir attendu.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2041,7 +2107,18 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Marceau a attendu. Puis il a parlé.</t>
+          <t>papa|Oui.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Aniss souffle un peu.
+narrateur|Sa main redescend, tout doux.
+narrateur|Le tapis reste chaud sous les genoux.
+enfant-m|J'ai attendu.
+maman|Bravo.
+maman|Tu as levé la main.
+papa|C'est du bon travail, Aniss.
+narrateur|Le fil doux chatouille encore.
+maman|Tu as parlé, après avoir attendu.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2069,7 +2146,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>Le coin école a trois envies. L'histoire, la chanson, ou le dessin ? On lève la main. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2233,7 +2310,11 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>narrateur|Le coin école a trois envies.
+maman|L'histoire, la chanson, ou le dessin ?
+papa|On lève la main.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2261,7 +2342,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Marceau attend. Puis il parle.</t>
+          <t>Maman ouvre un petit livre. La page sent le papier, tout sec. Un lapin blanc est dessiné, tout rond. Moi, je raconte le lapin. Maman parle jusqu'au bout. Aniss lève la main. Il attend. C'est ton tour, Aniss. Le lapin a de grandes oreilles. Oui. Merci d'avoir attendu. On attend. Puis on parle. Aniss touche la page, tout léger. Bravo. Le lapin blanc semble assis sur le tapis gris. Le tapis reste tout près. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2401,10 +2482,32 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Marceau attend. Puis il parle.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Maman ouvre un petit livre.
+narrateur|La page sent le papier, tout sec.
+narrateur|Un lapin blanc est dessiné, tout rond.
+maman|Moi, je raconte le lapin.
+narrateur|Maman parle jusqu'au bout.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+maman|C'est ton tour, Aniss.
+enfant-m|Le lapin a de grandes oreilles.
+papa|Oui.
+papa|Merci d'avoir attendu.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Aniss touche la page, tout léger.
+papa|Bravo.
+narrateur|Le lapin blanc semble assis sur le tapis gris.
+narrateur|Le tapis reste tout près.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>livre</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2429,7 +2532,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Trois peluches attendent, tout calmes. Léa, Tom, ou Sami ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2597,7 +2700,10 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout calmes.
+papa|Léa, Tom, ou Sami ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2625,7 +2731,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Léa. Il a attendu. Puis il a parlé, à le tapis, pendant l'histoire.</t>
+          <t>Aniss rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Aniss l'assoit contre le coussin. Léa, j'ai levé la main. J'ai attendu. Tu peux le dire à Léa. Papa et maman t'écoutent aussi. Aniss lisse la robe bleue. On attend. Puis on parle. La poupée Léa a un lapin blanc, collé au tablier. Aniss se souvient de le tapis. Il a vécu l'histoire, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2765,7 +2871,31 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à le tapis, pendant l'histoire.</t>
+          <t>narrateur|Aniss rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Aniss l'assoit contre le coussin.
+enfant-m|Léa, j'ai levé la main.
+enfant-m|J'ai attendu.
+maman|Tu peux le dire à Léa.
+maman|Papa et maman t'écoutent aussi.
+narrateur|Aniss lisse la robe bleue.
+papa|On attend.
+papa|Puis on parle.
+narrateur|La poupée Léa a un lapin blanc, collé au tablier.
+narrateur|Aniss se souvient de le tapis.
+narrateur|Il a vécu l'histoire, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2793,7 +2923,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi le tapis, l'histoire, et la poupée Léa. La poupée Léa s'endort contre le coussin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2933,7 +3063,13 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi le tapis, l'histoire, et la poupée Léa.
+narrateur|La poupée Léa s'endort contre le coussin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2961,7 +3097,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Tom. Il a attendu. Puis il a parlé, à le tapis, pendant l'histoire.</t>
+          <t>Aniss rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Aniss l'assoit tout droit. Tom, j'ai attendu. Puis j'ai parlé. Tu as bien fait. On lève la main. On attend. Aniss caresse l'oreille de l'ours. Bravo, Aniss. L'ours Tom a une page du livre, sous la patte. Aniss se souvient de le tapis. Il a vécu l'histoire, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3101,7 +3237,31 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à le tapis, pendant l'histoire.</t>
+          <t>narrateur|Aniss rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Aniss l'assoit tout droit.
+enfant-m|Tom, j'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait.
+papa|On lève la main.
+papa|On attend.
+narrateur|Aniss caresse l'oreille de l'ours.
+maman|Bravo, Aniss.
+narrateur|L'ours Tom a une page du livre, sous la patte.
+narrateur|Aniss se souvient de le tapis.
+narrateur|Il a vécu l'histoire, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3129,7 +3289,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi le tapis, l'histoire, et l'ours Tom. L'ours Tom baisse une oreille, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3269,7 +3429,13 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi le tapis, l'histoire, et l'ours Tom.
+narrateur|L'ours Tom baisse une oreille, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3297,7 +3463,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Sami. Il a attendu. Puis il a parlé, à le tapis, pendant l'histoire.</t>
+          <t>Aniss rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Aniss tient Sami contre son genou. Sami, j'ai levé la main. Tu as attendu. Puis tu as parlé. Je t'écoute. Aniss range une mèche de laine. On attend. Puis on parle. Le lion Sami écoute le lapin, tout sage. Aniss se souvient de le tapis. Il a vécu l'histoire, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3437,7 +3603,31 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à le tapis, pendant l'histoire.</t>
+          <t>narrateur|Aniss rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Aniss tient Sami contre son genou.
+enfant-m|Sami, j'ai levé la main.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+maman|Je t'écoute.
+narrateur|Aniss range une mèche de laine.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Le lion Sami écoute le lapin, tout sage.
+narrateur|Aniss se souvient de le tapis.
+narrateur|Il a vécu l'histoire, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3465,7 +3655,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi le tapis, l'histoire, et le lion Sami. Le lion Sami ferme un œil de bouton. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3605,7 +3795,13 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi le tapis, l'histoire, et le lion Sami.
+narrateur|Le lion Sami ferme un œil de bouton.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3633,7 +3829,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Marceau attend. Puis il parle.</t>
+          <t>Papa fredonne tout bas. La voix est ronde, tout calme. Aniss tapote le genou, tout doux. Moi, je chante d'abord. Papa chante jusqu'au bout. Aniss lève la main. Il attend. C'est ton tour. Je connais la chanson. Oui. Tu as attendu. On attend. Puis on parle. Aniss chante un tout petit bout. Bravo, Aniss. La chanson fait un petit écho, tout bas, sur le tapis. Le tapis reste tout près. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3773,10 +3969,32 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Marceau attend. Puis il parle.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Papa fredonne tout bas.
+narrateur|La voix est ronde, tout calme.
+narrateur|Aniss tapote le genou, tout doux.
+papa|Moi, je chante d'abord.
+narrateur|Papa chante jusqu'au bout.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+papa|C'est ton tour.
+enfant-m|Je connais la chanson.
+maman|Oui.
+maman|Tu as attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Aniss chante un tout petit bout.
+maman|Bravo, Aniss.
+narrateur|La chanson fait un petit écho, tout bas, sur le tapis.
+narrateur|Le tapis reste tout près.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>chanson</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3801,7 +4019,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Trois peluches attendent, tout calmes. Léa, Tom, ou Sami ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3969,7 +4187,10 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout calmes.
+papa|Léa, Tom, ou Sami ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3997,7 +4218,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Léa. Il a attendu. Puis il a parlé, à le tapis, pendant la chanson.</t>
+          <t>Aniss rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Aniss l'assoit contre le coussin. Léa, j'ai levé la main. J'ai attendu. Tu peux le dire à Léa. Papa et maman t'écoutent aussi. Aniss lisse la robe bleue. On attend. Puis on parle. La poupée Léa a un grelot, tout petit. Aniss se souvient de le tapis. Il a vécu la chanson, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4137,7 +4358,31 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à le tapis, pendant la chanson.</t>
+          <t>narrateur|Aniss rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Aniss l'assoit contre le coussin.
+enfant-m|Léa, j'ai levé la main.
+enfant-m|J'ai attendu.
+maman|Tu peux le dire à Léa.
+maman|Papa et maman t'écoutent aussi.
+narrateur|Aniss lisse la robe bleue.
+papa|On attend.
+papa|Puis on parle.
+narrateur|La poupée Léa a un grelot, tout petit.
+narrateur|Aniss se souvient de le tapis.
+narrateur|Il a vécu la chanson, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4165,7 +4410,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi le tapis, la chanson, et la poupée Léa. La poupée Léa s'endort contre le coussin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4305,7 +4550,13 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi le tapis, la chanson, et la poupée Léa.
+narrateur|La poupée Léa s'endort contre le coussin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4333,7 +4584,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Tom. Il a attendu. Puis il a parlé, à le tapis, pendant la chanson.</t>
+          <t>Aniss rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Aniss l'assoit tout droit. Tom, j'ai attendu. Puis j'ai parlé. Tu as bien fait. On lève la main. On attend. Aniss caresse l'oreille de l'ours. Bravo, Aniss. L'ours Tom tapote le tapis, en rythme. Aniss se souvient de le tapis. Il a vécu la chanson, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4473,7 +4724,31 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à le tapis, pendant la chanson.</t>
+          <t>narrateur|Aniss rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Aniss l'assoit tout droit.
+enfant-m|Tom, j'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait.
+papa|On lève la main.
+papa|On attend.
+narrateur|Aniss caresse l'oreille de l'ours.
+maman|Bravo, Aniss.
+narrateur|L'ours Tom tapote le tapis, en rythme.
+narrateur|Aniss se souvient de le tapis.
+narrateur|Il a vécu la chanson, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4501,7 +4776,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi le tapis, la chanson, et l'ours Tom. L'ours Tom baisse une oreille, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4641,7 +4916,13 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi le tapis, la chanson, et l'ours Tom.
+narrateur|L'ours Tom baisse une oreille, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4669,7 +4950,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Sami. Il a attendu. Puis il a parlé, à le tapis, pendant la chanson.</t>
+          <t>Aniss rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Aniss tient Sami contre son genou. Sami, j'ai levé la main. Tu as attendu. Puis tu as parlé. Je t'écoute. Aniss range une mèche de laine. On attend. Puis on parle. Le lion Sami a la crinière qui bouge, tout doux. Aniss se souvient de le tapis. Il a vécu la chanson, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4809,7 +5090,31 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à le tapis, pendant la chanson.</t>
+          <t>narrateur|Aniss rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Aniss tient Sami contre son genou.
+enfant-m|Sami, j'ai levé la main.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+maman|Je t'écoute.
+narrateur|Aniss range une mèche de laine.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Le lion Sami a la crinière qui bouge, tout doux.
+narrateur|Aniss se souvient de le tapis.
+narrateur|Il a vécu la chanson, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4837,7 +5142,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi le tapis, la chanson, et le lion Sami. Le lion Sami ferme un œil de bouton. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4977,7 +5282,13 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi le tapis, la chanson, et le lion Sami.
+narrateur|Le lion Sami ferme un œil de bouton.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5005,7 +5316,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Marceau attend. Puis il parle.</t>
+          <t>Aniss prend un crayon bleu. Le bois est lisse, un peu chaud. Une feuille attend, toute blanche. Moi, je dessine d'abord un rond. Maman parle, et elle dessine. Aniss lève la main. Il attend. C'est ton tour. Je dessine une maison. Oui. Merci d'avoir attendu. On attend. Puis on parle. Aniss trace un toit, tout doux. Bravo. Le crayon bleu roule un peu, sur le tapis rêche. Le tapis reste tout près. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5145,10 +5456,32 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Marceau attend. Puis il parle.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Aniss prend un crayon bleu.
+narrateur|Le bois est lisse, un peu chaud.
+narrateur|Une feuille attend, toute blanche.
+maman|Moi, je dessine d'abord un rond.
+narrateur|Maman parle, et elle dessine.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+maman|C'est ton tour.
+enfant-m|Je dessine une maison.
+papa|Oui.
+papa|Merci d'avoir attendu.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Aniss trace un toit, tout doux.
+papa|Bravo.
+narrateur|Le crayon bleu roule un peu, sur le tapis rêche.
+narrateur|Le tapis reste tout près.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5173,7 +5506,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Trois peluches attendent, tout calmes. Léa, Tom, ou Sami ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5341,7 +5674,10 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout calmes.
+papa|Léa, Tom, ou Sami ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5369,7 +5705,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Léa. Il a attendu. Puis il a parlé, à le tapis, pendant le dessin.</t>
+          <t>Aniss rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Aniss l'assoit contre le coussin. Léa, j'ai levé la main. J'ai attendu. Tu peux le dire à Léa. Papa et maman t'écoutent aussi. Aniss lisse la robe bleue. On attend. Puis on parle. La poupée Léa a un trait bleu, sur la robe. Aniss se souvient de le tapis. Il a vécu le dessin, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5509,7 +5845,31 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à le tapis, pendant le dessin.</t>
+          <t>narrateur|Aniss rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Aniss l'assoit contre le coussin.
+enfant-m|Léa, j'ai levé la main.
+enfant-m|J'ai attendu.
+maman|Tu peux le dire à Léa.
+maman|Papa et maman t'écoutent aussi.
+narrateur|Aniss lisse la robe bleue.
+papa|On attend.
+papa|Puis on parle.
+narrateur|La poupée Léa a un trait bleu, sur la robe.
+narrateur|Aniss se souvient de le tapis.
+narrateur|Il a vécu le dessin, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5537,7 +5897,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi le tapis, le dessin, et la poupée Léa. La poupée Léa s'endort contre le coussin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5677,7 +6037,13 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi le tapis, le dessin, et la poupée Léa.
+narrateur|La poupée Léa s'endort contre le coussin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5705,7 +6071,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Tom. Il a attendu. Puis il a parlé, à le tapis, pendant le dessin.</t>
+          <t>Aniss rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Aniss l'assoit tout droit. Tom, j'ai attendu. Puis j'ai parlé. Tu as bien fait. On lève la main. On attend. Aniss caresse l'oreille de l'ours. Bravo, Aniss. L'ours Tom a un crayon, trop grand, sous le bras. Aniss se souvient de le tapis. Il a vécu le dessin, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5845,7 +6211,31 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à le tapis, pendant le dessin.</t>
+          <t>narrateur|Aniss rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Aniss l'assoit tout droit.
+enfant-m|Tom, j'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait.
+papa|On lève la main.
+papa|On attend.
+narrateur|Aniss caresse l'oreille de l'ours.
+maman|Bravo, Aniss.
+narrateur|L'ours Tom a un crayon, trop grand, sous le bras.
+narrateur|Aniss se souvient de le tapis.
+narrateur|Il a vécu le dessin, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5873,7 +6263,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi le tapis, le dessin, et l'ours Tom. L'ours Tom baisse une oreille, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6013,7 +6403,13 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi le tapis, le dessin, et l'ours Tom.
+narrateur|L'ours Tom baisse une oreille, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6041,7 +6437,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Sami. Il a attendu. Puis il a parlé, à le tapis, pendant le dessin.</t>
+          <t>Aniss rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Aniss tient Sami contre son genou. Sami, j'ai levé la main. Tu as attendu. Puis tu as parlé. Je t'écoute. Aniss range une mèche de laine. On attend. Puis on parle. Le lion Sami a une maison bleue, sur le ventre. Aniss se souvient de le tapis. Il a vécu le dessin, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6181,7 +6577,31 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à le tapis, pendant le dessin.</t>
+          <t>narrateur|Aniss rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Aniss tient Sami contre son genou.
+enfant-m|Sami, j'ai levé la main.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+maman|Je t'écoute.
+narrateur|Aniss range une mèche de laine.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Le lion Sami a une maison bleue, sur le ventre.
+narrateur|Aniss se souvient de le tapis.
+narrateur|Il a vécu le dessin, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6209,7 +6629,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi le tapis, le dessin, et le lion Sami. Le lion Sami ferme un œil de bouton. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6349,7 +6769,13 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi le tapis, le dessin, et le lion Sami.
+narrateur|Le lion Sami ferme un œil de bouton.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6377,7 +6803,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>À la table, Marceau lève la main. Il attend. Puis il parle.</t>
+          <t>Aniss tire une chaise près de la table. Le bois est lisse, un peu froid. Un crayon bleu roule, tout lentement. Une feuille blanche attend, toute plate. Assieds-toi, Aniss. Moi, je raconte le crayon. Maman parle jusqu'au bout. Aniss lève la main. Il attend. Le crayon est bleu. Oui. Merci d'avoir attendu. On attend. Puis on parle. Aniss pose la main à plat, tout calme. Bravo. Tu as levé la main. Puis tu as parlé. Le crayon bleu reste près de la feuille. On peut lever la main, à la table aussi.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6517,10 +6943,33 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|À la table, Marceau lève la main. Il attend. Puis il parle.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Aniss tire une chaise près de la table.
+narrateur|Le bois est lisse, un peu froid.
+narrateur|Un crayon bleu roule, tout lentement.
+narrateur|Une feuille blanche attend, toute plate.
+maman|Assieds-toi, Aniss.
+maman|Moi, je raconte le crayon.
+narrateur|Maman parle jusqu'au bout.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|Le crayon est bleu.
+papa|Oui.
+papa|Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Aniss pose la main à plat, tout calme.
+maman|Bravo.
+maman|Tu as levé la main.
+maman|Puis tu as parlé.
+narrateur|Le crayon bleu reste près de la feuille.
+papa|On peut lever la main, à la table aussi.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6545,7 +6994,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>À la table, que fait Marceau d'abord ?</t>
+          <t>À la table, Aniss veut parler. Il fait quoi d'abord ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6701,7 +7150,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|À la table, que fait Marceau d'abord ?</t>
+          <t>narrateur|À la table, Aniss veut parler.
+maman|Il fait quoi d'abord ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6729,7 +7179,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Attendre, puis parler.</t>
+          <t>Oui. On lève la main. On attend. Puis on parle. Aniss pose le crayon, tout droit. La feuille est encore blanche, toute plate. J'ai levé la main. Bravo, Aniss. Tu as attendu ton tour. Le bois de la table est un peu froid. C'est du bon travail. On continue ensemble.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6873,7 +7323,18 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Attendre, puis parler.</t>
+          <t>maman|Oui.
+maman|On lève la main.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Aniss pose le crayon, tout droit.
+narrateur|La feuille est encore blanche, toute plate.
+enfant-m|J'ai levé la main.
+papa|Bravo, Aniss.
+papa|Tu as attendu ton tour.
+narrateur|Le bois de la table est un peu froid.
+maman|C'est du bon travail.
+maman|On continue ensemble.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6901,7 +7362,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>Le coin école a trois envies. L'histoire, la chanson, ou le dessin ? On lève la main. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7065,7 +7526,11 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>narrateur|Le coin école a trois envies.
+maman|L'histoire, la chanson, ou le dessin ?
+papa|On lève la main.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7093,7 +7558,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Marceau attend. Puis il parle.</t>
+          <t>Maman ouvre un petit livre. La page sent le papier, tout sec. Un lapin blanc est dessiné, tout rond. Moi, je raconte le lapin. Maman parle jusqu'au bout. Aniss lève la main. Il attend. C'est ton tour, Aniss. Le lapin a de grandes oreilles. Oui. Merci d'avoir attendu. On attend. Puis on parle. Aniss touche la page, tout léger. Bravo. Le livre est ouvert, tout plat, sur la table. La table reste tout près. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7233,10 +7698,32 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Marceau attend. Puis il parle.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Maman ouvre un petit livre.
+narrateur|La page sent le papier, tout sec.
+narrateur|Un lapin blanc est dessiné, tout rond.
+maman|Moi, je raconte le lapin.
+narrateur|Maman parle jusqu'au bout.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+maman|C'est ton tour, Aniss.
+enfant-m|Le lapin a de grandes oreilles.
+papa|Oui.
+papa|Merci d'avoir attendu.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Aniss touche la page, tout léger.
+papa|Bravo.
+narrateur|Le livre est ouvert, tout plat, sur la table.
+narrateur|La table reste tout près.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>livre</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7261,7 +7748,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Trois peluches attendent, tout calmes. Léa, Tom, ou Sami ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7429,7 +7916,10 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout calmes.
+papa|Léa, Tom, ou Sami ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7457,7 +7947,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la table, pendant l'histoire.</t>
+          <t>Aniss rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Aniss l'assoit contre le coussin. Léa, j'ai levé la main. J'ai attendu. Tu peux le dire à Léa. Papa et maman t'écoutent aussi. Aniss lisse la robe bleue. On attend. Puis on parle. La poupée Léa est assise près du livre, tout droite. Aniss se souvient de la table. Il a vécu l'histoire, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7597,7 +8087,31 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la table, pendant l'histoire.</t>
+          <t>narrateur|Aniss rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Aniss l'assoit contre le coussin.
+enfant-m|Léa, j'ai levé la main.
+enfant-m|J'ai attendu.
+maman|Tu peux le dire à Léa.
+maman|Papa et maman t'écoutent aussi.
+narrateur|Aniss lisse la robe bleue.
+papa|On attend.
+papa|Puis on parle.
+narrateur|La poupée Léa est assise près du livre, tout droite.
+narrateur|Aniss se souvient de la table.
+narrateur|Il a vécu l'histoire, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7625,7 +8139,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la table, l'histoire, et la poupée Léa. La poupée Léa s'endort contre le coussin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7765,7 +8279,13 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la table, l'histoire, et la poupée Léa.
+narrateur|La poupée Léa s'endort contre le coussin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7793,7 +8313,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la table, pendant l'histoire.</t>
+          <t>Aniss rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Aniss l'assoit tout droit. Tom, j'ai attendu. Puis j'ai parlé. Tu as bien fait. On lève la main. On attend. Aniss caresse l'oreille de l'ours. Bravo, Aniss. L'ours Tom pose le nez sur le lapin blanc. Aniss se souvient de la table. Il a vécu l'histoire, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7933,7 +8453,31 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la table, pendant l'histoire.</t>
+          <t>narrateur|Aniss rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Aniss l'assoit tout droit.
+enfant-m|Tom, j'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait.
+papa|On lève la main.
+papa|On attend.
+narrateur|Aniss caresse l'oreille de l'ours.
+maman|Bravo, Aniss.
+narrateur|L'ours Tom pose le nez sur le lapin blanc.
+narrateur|Aniss se souvient de la table.
+narrateur|Il a vécu l'histoire, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7961,7 +8505,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la table, l'histoire, et l'ours Tom. L'ours Tom baisse une oreille, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8101,7 +8645,13 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la table, l'histoire, et l'ours Tom.
+narrateur|L'ours Tom baisse une oreille, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8129,7 +8679,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la table, pendant l'histoire.</t>
+          <t>Aniss rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Aniss tient Sami contre son genou. Sami, j'ai levé la main. Tu as attendu. Puis tu as parlé. Je t'écoute. Aniss range une mèche de laine. On attend. Puis on parle. Le lion Sami a une miette de papier, dans la laine. Aniss se souvient de la table. Il a vécu l'histoire, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8269,7 +8819,31 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la table, pendant l'histoire.</t>
+          <t>narrateur|Aniss rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Aniss tient Sami contre son genou.
+enfant-m|Sami, j'ai levé la main.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+maman|Je t'écoute.
+narrateur|Aniss range une mèche de laine.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Le lion Sami a une miette de papier, dans la laine.
+narrateur|Aniss se souvient de la table.
+narrateur|Il a vécu l'histoire, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8297,7 +8871,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la table, l'histoire, et le lion Sami. Le lion Sami ferme un œil de bouton. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8437,7 +9011,13 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la table, l'histoire, et le lion Sami.
+narrateur|Le lion Sami ferme un œil de bouton.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8465,7 +9045,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Marceau attend. Puis il parle.</t>
+          <t>Papa fredonne tout bas. La voix est ronde, tout calme. Aniss tapote le genou, tout doux. Moi, je chante d'abord. Papa chante jusqu'au bout. Aniss lève la main. Il attend. C'est ton tour. Je connais la chanson. Oui. Tu as attendu. On attend. Puis on parle. Aniss chante un tout petit bout. Bravo, Aniss. Le crayon bleu tapote la table, en rythme. La table reste tout près. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8605,10 +9185,32 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Marceau attend. Puis il parle.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Papa fredonne tout bas.
+narrateur|La voix est ronde, tout calme.
+narrateur|Aniss tapote le genou, tout doux.
+papa|Moi, je chante d'abord.
+narrateur|Papa chante jusqu'au bout.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+papa|C'est ton tour.
+enfant-m|Je connais la chanson.
+maman|Oui.
+maman|Tu as attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Aniss chante un tout petit bout.
+maman|Bravo, Aniss.
+narrateur|Le crayon bleu tapote la table, en rythme.
+narrateur|La table reste tout près.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>chanson</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8633,7 +9235,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Trois peluches attendent, tout calmes. Léa, Tom, ou Sami ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8801,7 +9403,10 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout calmes.
+papa|Léa, Tom, ou Sami ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8829,7 +9434,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la table, pendant la chanson.</t>
+          <t>Aniss rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Aniss l'assoit contre le coussin. Léa, j'ai levé la main. J'ai attendu. Tu peux le dire à Léa. Papa et maman t'écoutent aussi. Aniss lisse la robe bleue. On attend. Puis on parle. La poupée Léa se balance, tout léger, sur la chaise. Aniss se souvient de la table. Il a vécu la chanson, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8969,7 +9574,31 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la table, pendant la chanson.</t>
+          <t>narrateur|Aniss rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Aniss l'assoit contre le coussin.
+enfant-m|Léa, j'ai levé la main.
+enfant-m|J'ai attendu.
+maman|Tu peux le dire à Léa.
+maman|Papa et maman t'écoutent aussi.
+narrateur|Aniss lisse la robe bleue.
+papa|On attend.
+papa|Puis on parle.
+narrateur|La poupée Léa se balance, tout léger, sur la chaise.
+narrateur|Aniss se souvient de la table.
+narrateur|Il a vécu la chanson, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -8997,7 +9626,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la table, la chanson, et la poupée Léa. La poupée Léa s'endort contre le coussin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9137,7 +9766,13 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la table, la chanson, et la poupée Léa.
+narrateur|La poupée Léa s'endort contre le coussin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9165,7 +9800,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la table, pendant la chanson.</t>
+          <t>Aniss rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Aniss l'assoit tout droit. Tom, j'ai attendu. Puis j'ai parlé. Tu as bien fait. On lève la main. On attend. Aniss caresse l'oreille de l'ours. Bravo, Aniss. L'ours Tom a l'oreille pliée, comme une note. Aniss se souvient de la table. Il a vécu la chanson, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9305,7 +9940,31 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la table, pendant la chanson.</t>
+          <t>narrateur|Aniss rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Aniss l'assoit tout droit.
+enfant-m|Tom, j'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait.
+papa|On lève la main.
+papa|On attend.
+narrateur|Aniss caresse l'oreille de l'ours.
+maman|Bravo, Aniss.
+narrateur|L'ours Tom a l'oreille pliée, comme une note.
+narrateur|Aniss se souvient de la table.
+narrateur|Il a vécu la chanson, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9333,7 +9992,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la table, la chanson, et l'ours Tom. L'ours Tom baisse une oreille, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9473,7 +10132,13 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la table, la chanson, et l'ours Tom.
+narrateur|L'ours Tom baisse une oreille, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9501,7 +10166,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la table, pendant la chanson.</t>
+          <t>Aniss rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Aniss tient Sami contre son genou. Sami, j'ai levé la main. Tu as attendu. Puis tu as parlé. Je t'écoute. Aniss range une mèche de laine. On attend. Puis on parle. Le lion Sami écoute la table, tout calme. Aniss se souvient de la table. Il a vécu la chanson, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9641,7 +10306,31 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la table, pendant la chanson.</t>
+          <t>narrateur|Aniss rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Aniss tient Sami contre son genou.
+enfant-m|Sami, j'ai levé la main.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+maman|Je t'écoute.
+narrateur|Aniss range une mèche de laine.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Le lion Sami écoute la table, tout calme.
+narrateur|Aniss se souvient de la table.
+narrateur|Il a vécu la chanson, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9669,7 +10358,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la table, la chanson, et le lion Sami. Le lion Sami ferme un œil de bouton. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9809,7 +10498,13 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la table, la chanson, et le lion Sami.
+narrateur|Le lion Sami ferme un œil de bouton.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9837,7 +10532,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Marceau attend. Puis il parle.</t>
+          <t>Aniss prend un crayon bleu. Le bois est lisse, un peu chaud. Une feuille attend, toute blanche. Moi, je dessine d'abord un rond. Maman parle, et elle dessine. Aniss lève la main. Il attend. C'est ton tour. Je dessine une maison. Oui. Merci d'avoir attendu. On attend. Puis on parle. Aniss trace un toit, tout doux. Bravo. La maison bleue grandit, sur la feuille blanche. La table reste tout près. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9977,10 +10672,32 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Marceau attend. Puis il parle.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Aniss prend un crayon bleu.
+narrateur|Le bois est lisse, un peu chaud.
+narrateur|Une feuille attend, toute blanche.
+maman|Moi, je dessine d'abord un rond.
+narrateur|Maman parle, et elle dessine.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+maman|C'est ton tour.
+enfant-m|Je dessine une maison.
+papa|Oui.
+papa|Merci d'avoir attendu.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Aniss trace un toit, tout doux.
+papa|Bravo.
+narrateur|La maison bleue grandit, sur la feuille blanche.
+narrateur|La table reste tout près.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10005,7 +10722,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Trois peluches attendent, tout calmes. Léa, Tom, ou Sami ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10173,7 +10890,10 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout calmes.
+papa|Léa, Tom, ou Sami ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10201,7 +10921,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la table, pendant le dessin.</t>
+          <t>Aniss rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Aniss l'assoit contre le coussin. Léa, j'ai levé la main. J'ai attendu. Tu peux le dire à Léa. Papa et maman t'écoutent aussi. Aniss lisse la robe bleue. On attend. Puis on parle. La poupée Léa tient le crayon bleu, trop lourd. Aniss se souvient de la table. Il a vécu le dessin, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10341,7 +11061,31 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la table, pendant le dessin.</t>
+          <t>narrateur|Aniss rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Aniss l'assoit contre le coussin.
+enfant-m|Léa, j'ai levé la main.
+enfant-m|J'ai attendu.
+maman|Tu peux le dire à Léa.
+maman|Papa et maman t'écoutent aussi.
+narrateur|Aniss lisse la robe bleue.
+papa|On attend.
+papa|Puis on parle.
+narrateur|La poupée Léa tient le crayon bleu, trop lourd.
+narrateur|Aniss se souvient de la table.
+narrateur|Il a vécu le dessin, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10369,7 +11113,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la table, le dessin, et la poupée Léa. La poupée Léa s'endort contre le coussin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10509,7 +11253,13 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la table, le dessin, et la poupée Léa.
+narrateur|La poupée Léa s'endort contre le coussin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10537,7 +11287,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la table, pendant le dessin.</t>
+          <t>Aniss rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Aniss l'assoit tout droit. Tom, j'ai attendu. Puis j'ai parlé. Tu as bien fait. On lève la main. On attend. Aniss caresse l'oreille de l'ours. Bravo, Aniss. L'ours Tom a un rond bleu, sur la patte. Aniss se souvient de la table. Il a vécu le dessin, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10677,7 +11427,31 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la table, pendant le dessin.</t>
+          <t>narrateur|Aniss rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Aniss l'assoit tout droit.
+enfant-m|Tom, j'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait.
+papa|On lève la main.
+papa|On attend.
+narrateur|Aniss caresse l'oreille de l'ours.
+maman|Bravo, Aniss.
+narrateur|L'ours Tom a un rond bleu, sur la patte.
+narrateur|Aniss se souvient de la table.
+narrateur|Il a vécu le dessin, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10705,7 +11479,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la table, le dessin, et l'ours Tom. L'ours Tom baisse une oreille, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10845,7 +11619,13 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la table, le dessin, et l'ours Tom.
+narrateur|L'ours Tom baisse une oreille, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10873,7 +11653,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la table, pendant le dessin.</t>
+          <t>Aniss rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Aniss tient Sami contre son genou. Sami, j'ai levé la main. Tu as attendu. Puis tu as parlé. Je t'écoute. Aniss range une mèche de laine. On attend. Puis on parle. Le lion Sami veille près de la feuille blanche. Aniss se souvient de la table. Il a vécu le dessin, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11013,7 +11793,31 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la table, pendant le dessin.</t>
+          <t>narrateur|Aniss rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Aniss tient Sami contre son genou.
+enfant-m|Sami, j'ai levé la main.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+maman|Je t'écoute.
+narrateur|Aniss range une mèche de laine.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Le lion Sami veille près de la feuille blanche.
+narrateur|Aniss se souvient de la table.
+narrateur|Il a vécu le dessin, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11041,7 +11845,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la table, le dessin, et le lion Sami. Le lion Sami ferme un œil de bouton. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11181,7 +11985,13 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la table, le dessin, et le lion Sami.
+narrateur|Le lion Sami ferme un œil de bouton.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11209,7 +12019,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Près de la fenêtre, Marceau lève la main. Il attend. Puis il parle.</t>
+          <t>Aniss s'approche de la fenêtre. La vitre est embuée, tout bas. Une goutte dessine un trait, tout brillant. Dehors, un toit brille, tout mouillé. Regarde, Aniss. Moi, je raconte la goutte. Papa parle, tout calme. Aniss lève la main. Il attend. La goutte descend tout doucement. Oui. C'est ton tour. On a attendu. Puis on parle. Aniss trace un rond sur la buée, tout léger. Bravo, Aniss. Tu as attendu. Puis tu as parlé. Le rond s'efface, tout lentement. On peut lever la main, près de la fenêtre aussi.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11349,10 +12159,33 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Près de la fenêtre, Marceau lève la main. Il attend. Puis il parle.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Aniss s'approche de la fenêtre.
+narrateur|La vitre est embuée, tout bas.
+narrateur|Une goutte dessine un trait, tout brillant.
+narrateur|Dehors, un toit brille, tout mouillé.
+papa|Regarde, Aniss.
+papa|Moi, je raconte la goutte.
+narrateur|Papa parle, tout calme.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+enfant-m|La goutte descend tout doucement.
+maman|Oui.
+maman|C'est ton tour.
+maman|On a attendu.
+maman|Puis on parle.
+narrateur|Aniss trace un rond sur la buée, tout léger.
+papa|Bravo, Aniss.
+papa|Tu as attendu.
+papa|Puis tu as parlé.
+narrateur|Le rond s'efface, tout lentement.
+maman|On peut lever la main, près de la fenêtre aussi.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>goutte</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11377,7 +12210,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Près de la fenêtre, que fait Marceau d'abord ?</t>
+          <t>Près de la fenêtre, Aniss veut parler. Il fait quoi d'abord ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11533,7 +12366,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Près de la fenêtre, que fait Marceau d'abord ?</t>
+          <t>narrateur|Près de la fenêtre, Aniss veut parler.
+papa|Il fait quoi d'abord ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11561,7 +12395,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Marceau a levé la main. Il a attendu. Puis il a parlé.</t>
+          <t>Oui. On attend. Puis on parle. Aniss essuie un peu de buée, tout doux. Le toit mouillé brille encore. J'ai attendu. Puis j'ai parlé. Bravo. Tu as levé la main. C'est du bon travail, Aniss. Une autre goutte glisse, tout loin. On peut lever la main, encore.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11705,7 +12539,18 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Marceau a levé la main. Il a attendu. Puis il a parlé.</t>
+          <t>papa|Oui.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Aniss essuie un peu de buée, tout doux.
+narrateur|Le toit mouillé brille encore.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo.
+maman|Tu as levé la main.
+papa|C'est du bon travail, Aniss.
+narrateur|Une autre goutte glisse, tout loin.
+maman|On peut lever la main, encore.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11733,7 +12578,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>Le coin école a trois envies. L'histoire, la chanson, ou le dessin ? On lève la main. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11897,7 +12742,11 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>narrateur|Le coin école a trois envies.
+maman|L'histoire, la chanson, ou le dessin ?
+papa|On lève la main.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11925,7 +12774,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Marceau attend. Puis il parle.</t>
+          <t>Maman ouvre un petit livre. La page sent le papier, tout sec. Un lapin blanc est dessiné, tout rond. Moi, je raconte le lapin. Maman parle jusqu'au bout. Aniss lève la main. Il attend. C'est ton tour, Aniss. Le lapin a de grandes oreilles. Oui. Merci d'avoir attendu. On attend. Puis on parle. Aniss touche la page, tout léger. Bravo. Le lapin blanc regarde la goutte, sur la vitre. La fenêtre reste tout près. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12065,10 +12914,32 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Marceau attend. Puis il parle.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Maman ouvre un petit livre.
+narrateur|La page sent le papier, tout sec.
+narrateur|Un lapin blanc est dessiné, tout rond.
+maman|Moi, je raconte le lapin.
+narrateur|Maman parle jusqu'au bout.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+maman|C'est ton tour, Aniss.
+enfant-m|Le lapin a de grandes oreilles.
+papa|Oui.
+papa|Merci d'avoir attendu.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Aniss touche la page, tout léger.
+papa|Bravo.
+narrateur|Le lapin blanc regarde la goutte, sur la vitre.
+narrateur|La fenêtre reste tout près.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>livre</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12093,7 +12964,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Trois peluches attendent, tout calmes. Léa, Tom, ou Sami ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12261,7 +13132,10 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout calmes.
+papa|Léa, Tom, ou Sami ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12289,7 +13163,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la fenêtre, pendant l'histoire.</t>
+          <t>Aniss rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Aniss l'assoit contre le coussin. Léa, j'ai levé la main. J'ai attendu. Tu peux le dire à Léa. Papa et maman t'écoutent aussi. Aniss lisse la robe bleue. On attend. Puis on parle. La poupée Léa regarde la goutte, tout près. Aniss se souvient de la fenêtre. Il a vécu l'histoire, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12429,7 +13303,31 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la fenêtre, pendant l'histoire.</t>
+          <t>narrateur|Aniss rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Aniss l'assoit contre le coussin.
+enfant-m|Léa, j'ai levé la main.
+enfant-m|J'ai attendu.
+maman|Tu peux le dire à Léa.
+maman|Papa et maman t'écoutent aussi.
+narrateur|Aniss lisse la robe bleue.
+papa|On attend.
+papa|Puis on parle.
+narrateur|La poupée Léa regarde la goutte, tout près.
+narrateur|Aniss se souvient de la fenêtre.
+narrateur|Il a vécu l'histoire, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12457,7 +13355,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la fenêtre, l'histoire, et la poupée Léa. La poupée Léa s'endort contre le coussin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12597,7 +13495,13 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la fenêtre, l'histoire, et la poupée Léa.
+narrateur|La poupée Léa s'endort contre le coussin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12625,7 +13529,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la fenêtre, pendant l'histoire.</t>
+          <t>Aniss rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Aniss l'assoit tout droit. Tom, j'ai attendu. Puis j'ai parlé. Tu as bien fait. On lève la main. On attend. Aniss caresse l'oreille de l'ours. Bravo, Aniss. L'ours Tom a un peu de buée, sur le nez. Aniss se souvient de la fenêtre. Il a vécu l'histoire, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12765,7 +13669,31 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la fenêtre, pendant l'histoire.</t>
+          <t>narrateur|Aniss rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Aniss l'assoit tout droit.
+enfant-m|Tom, j'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait.
+papa|On lève la main.
+papa|On attend.
+narrateur|Aniss caresse l'oreille de l'ours.
+maman|Bravo, Aniss.
+narrateur|L'ours Tom a un peu de buée, sur le nez.
+narrateur|Aniss se souvient de la fenêtre.
+narrateur|Il a vécu l'histoire, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12793,7 +13721,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la fenêtre, l'histoire, et l'ours Tom. L'ours Tom baisse une oreille, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12933,7 +13861,13 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la fenêtre, l'histoire, et l'ours Tom.
+narrateur|L'ours Tom baisse une oreille, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12961,7 +13895,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la fenêtre, pendant l'histoire.</t>
+          <t>Aniss rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Aniss tient Sami contre son genou. Sami, j'ai levé la main. Tu as attendu. Puis tu as parlé. Je t'écoute. Aniss range une mèche de laine. On attend. Puis on parle. Le lion Sami suit le trait sur la vitre. Aniss se souvient de la fenêtre. Il a vécu l'histoire, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13101,7 +14035,31 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la fenêtre, pendant l'histoire.</t>
+          <t>narrateur|Aniss rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Aniss tient Sami contre son genou.
+enfant-m|Sami, j'ai levé la main.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+maman|Je t'écoute.
+narrateur|Aniss range une mèche de laine.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Le lion Sami suit le trait sur la vitre.
+narrateur|Aniss se souvient de la fenêtre.
+narrateur|Il a vécu l'histoire, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13129,7 +14087,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la fenêtre, l'histoire, et le lion Sami. Le lion Sami ferme un œil de bouton. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13269,7 +14227,13 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la fenêtre, l'histoire, et le lion Sami.
+narrateur|Le lion Sami ferme un œil de bouton.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13297,7 +14261,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Marceau attend. Puis il parle.</t>
+          <t>Papa fredonne tout bas. La voix est ronde, tout calme. Aniss tapote le genou, tout doux. Moi, je chante d'abord. Papa chante jusqu'au bout. Aniss lève la main. Il attend. C'est ton tour. Je connais la chanson. Oui. Tu as attendu. On attend. Puis on parle. Aniss chante un tout petit bout. Bravo, Aniss. La chanson suit la goutte, tout lentement. La fenêtre reste tout près. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13437,10 +14401,32 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Marceau attend. Puis il parle.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Papa fredonne tout bas.
+narrateur|La voix est ronde, tout calme.
+narrateur|Aniss tapote le genou, tout doux.
+papa|Moi, je chante d'abord.
+narrateur|Papa chante jusqu'au bout.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+papa|C'est ton tour.
+enfant-m|Je connais la chanson.
+maman|Oui.
+maman|Tu as attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Aniss chante un tout petit bout.
+maman|Bravo, Aniss.
+narrateur|La chanson suit la goutte, tout lentement.
+narrateur|La fenêtre reste tout près.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>chanson</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13465,7 +14451,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Trois peluches attendent, tout calmes. Léa, Tom, ou Sami ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13633,7 +14619,10 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout calmes.
+papa|Léa, Tom, ou Sami ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13661,7 +14650,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la fenêtre, pendant la chanson.</t>
+          <t>Aniss rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Aniss l'assoit contre le coussin. Léa, j'ai levé la main. J'ai attendu. Tu peux le dire à Léa. Papa et maman t'écoutent aussi. Aniss lisse la robe bleue. On attend. Puis on parle. La poupée Léa a une goutte, sur le bouton. Aniss se souvient de la fenêtre. Il a vécu la chanson, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13801,7 +14790,31 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la fenêtre, pendant la chanson.</t>
+          <t>narrateur|Aniss rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Aniss l'assoit contre le coussin.
+enfant-m|Léa, j'ai levé la main.
+enfant-m|J'ai attendu.
+maman|Tu peux le dire à Léa.
+maman|Papa et maman t'écoutent aussi.
+narrateur|Aniss lisse la robe bleue.
+papa|On attend.
+papa|Puis on parle.
+narrateur|La poupée Léa a une goutte, sur le bouton.
+narrateur|Aniss se souvient de la fenêtre.
+narrateur|Il a vécu la chanson, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13829,7 +14842,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la fenêtre, la chanson, et la poupée Léa. La poupée Léa s'endort contre le coussin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13969,7 +14982,13 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la fenêtre, la chanson, et la poupée Léa.
+narrateur|La poupée Léa s'endort contre le coussin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13997,7 +15016,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la fenêtre, pendant la chanson.</t>
+          <t>Aniss rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Aniss l'assoit tout droit. Tom, j'ai attendu. Puis j'ai parlé. Tu as bien fait. On lève la main. On attend. Aniss caresse l'oreille de l'ours. Bravo, Aniss. L'ours Tom écoute la pluie, tout brun. Aniss se souvient de la fenêtre. Il a vécu la chanson, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14137,7 +15156,31 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la fenêtre, pendant la chanson.</t>
+          <t>narrateur|Aniss rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Aniss l'assoit tout droit.
+enfant-m|Tom, j'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait.
+papa|On lève la main.
+papa|On attend.
+narrateur|Aniss caresse l'oreille de l'ours.
+maman|Bravo, Aniss.
+narrateur|L'ours Tom écoute la pluie, tout brun.
+narrateur|Aniss se souvient de la fenêtre.
+narrateur|Il a vécu la chanson, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14165,7 +15208,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la fenêtre, la chanson, et l'ours Tom. L'ours Tom baisse une oreille, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14305,7 +15348,13 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la fenêtre, la chanson, et l'ours Tom.
+narrateur|L'ours Tom baisse une oreille, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14333,7 +15382,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la fenêtre, pendant la chanson.</t>
+          <t>Aniss rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Aniss tient Sami contre son genou. Sami, j'ai levé la main. Tu as attendu. Puis tu as parlé. Je t'écoute. Aniss range une mèche de laine. On attend. Puis on parle. Le lion Sami a la crinière un peu humide. Aniss se souvient de la fenêtre. Il a vécu la chanson, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14473,7 +15522,31 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la fenêtre, pendant la chanson.</t>
+          <t>narrateur|Aniss rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Aniss tient Sami contre son genou.
+enfant-m|Sami, j'ai levé la main.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+maman|Je t'écoute.
+narrateur|Aniss range une mèche de laine.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Le lion Sami a la crinière un peu humide.
+narrateur|Aniss se souvient de la fenêtre.
+narrateur|Il a vécu la chanson, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14501,7 +15574,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la fenêtre, la chanson, et le lion Sami. Le lion Sami ferme un œil de bouton. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14641,7 +15714,13 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la fenêtre, la chanson, et le lion Sami.
+narrateur|Le lion Sami ferme un œil de bouton.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14669,7 +15748,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Marceau attend. Puis il parle.</t>
+          <t>Aniss prend un crayon bleu. Le bois est lisse, un peu chaud. Une feuille attend, toute blanche. Moi, je dessine d'abord un rond. Maman parle, et elle dessine. Aniss lève la main. Il attend. C'est ton tour. Je dessine une maison. Oui. Merci d'avoir attendu. On attend. Puis on parle. Aniss trace un toit, tout doux. Bravo. La maison bleue a une fenêtre, comme la vraie. La fenêtre reste tout près. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14809,10 +15888,32 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Marceau attend. Puis il parle.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Aniss prend un crayon bleu.
+narrateur|Le bois est lisse, un peu chaud.
+narrateur|Une feuille attend, toute blanche.
+maman|Moi, je dessine d'abord un rond.
+narrateur|Maman parle, et elle dessine.
+narrateur|Aniss lève la main.
+narrateur|Il attend.
+maman|C'est ton tour.
+enfant-m|Je dessine une maison.
+papa|Oui.
+papa|Merci d'avoir attendu.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Aniss trace un toit, tout doux.
+papa|Bravo.
+narrateur|La maison bleue a une fenêtre, comme la vraie.
+narrateur|La fenêtre reste tout près.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14837,7 +15938,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Trois peluches attendent, tout calmes. Léa, Tom, ou Sami ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15005,7 +16106,10 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout calmes.
+papa|Léa, Tom, ou Sami ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15033,7 +16137,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la fenêtre, pendant le dessin.</t>
+          <t>Aniss rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Aniss l'assoit contre le coussin. Léa, j'ai levé la main. J'ai attendu. Tu peux le dire à Léa. Papa et maman t'écoutent aussi. Aniss lisse la robe bleue. On attend. Puis on parle. La poupée Léa a une maison, près de la vitre. Aniss se souvient de la fenêtre. Il a vécu le dessin, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15173,7 +16277,31 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Léa. Il a attendu. Puis il a parlé, à la fenêtre, pendant le dessin.</t>
+          <t>narrateur|Aniss rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Aniss l'assoit contre le coussin.
+enfant-m|Léa, j'ai levé la main.
+enfant-m|J'ai attendu.
+maman|Tu peux le dire à Léa.
+maman|Papa et maman t'écoutent aussi.
+narrateur|Aniss lisse la robe bleue.
+papa|On attend.
+papa|Puis on parle.
+narrateur|La poupée Léa a une maison, près de la vitre.
+narrateur|Aniss se souvient de la fenêtre.
+narrateur|Il a vécu le dessin, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15201,7 +16329,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la fenêtre, le dessin, et la poupée Léa. La poupée Léa s'endort contre le coussin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15341,7 +16469,13 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la fenêtre, le dessin, et la poupée Léa.
+narrateur|La poupée Léa s'endort contre le coussin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15369,7 +16503,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la fenêtre, pendant le dessin.</t>
+          <t>Aniss rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Aniss l'assoit tout droit. Tom, j'ai attendu. Puis j'ai parlé. Tu as bien fait. On lève la main. On attend. Aniss caresse l'oreille de l'ours. Bravo, Aniss. L'ours Tom a un toit bleu, comme dehors. Aniss se souvient de la fenêtre. Il a vécu le dessin, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15509,7 +16643,31 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Tom. Il a attendu. Puis il a parlé, à la fenêtre, pendant le dessin.</t>
+          <t>narrateur|Aniss rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Aniss l'assoit tout droit.
+enfant-m|Tom, j'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait.
+papa|On lève la main.
+papa|On attend.
+narrateur|Aniss caresse l'oreille de l'ours.
+maman|Bravo, Aniss.
+narrateur|L'ours Tom a un toit bleu, comme dehors.
+narrateur|Aniss se souvient de la fenêtre.
+narrateur|Il a vécu le dessin, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15537,7 +16695,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la fenêtre, le dessin, et l'ours Tom. L'ours Tom baisse une oreille, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15677,7 +16835,13 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la fenêtre, le dessin, et l'ours Tom.
+narrateur|L'ours Tom baisse une oreille, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15705,7 +16869,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la fenêtre, pendant le dessin.</t>
+          <t>Aniss rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Aniss tient Sami contre son genou. Sami, j'ai levé la main. Tu as attendu. Puis tu as parlé. Je t'écoute. Aniss range une mèche de laine. On attend. Puis on parle. Le lion Sami a un rond de buée, sur la laine. Aniss se souvient de la fenêtre. Il a vécu le dessin, tout près. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Tu as bien fait d'attendre. On attend. Puis on parle. Bravo, Aniss. C'est du bon travail. Merci, papa. Merci, maman. Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15845,7 +17009,31 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Marceau rejoint Sami. Il a attendu. Puis il a parlé, à la fenêtre, pendant le dessin.</t>
+          <t>narrateur|Aniss rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Aniss tient Sami contre son genou.
+enfant-m|Sami, j'ai levé la main.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+maman|Je t'écoute.
+narrateur|Aniss range une mèche de laine.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Le lion Sami a un rond de buée, sur la laine.
+narrateur|Aniss se souvient de la fenêtre.
+narrateur|Il a vécu le dessin, tout près.
+enfant-m|J'ai levé la main.
+enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+papa|Tu as bien fait d'attendre.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Aniss.
+papa|C'est du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Aniss pose le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15873,7 +17061,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai parlé. Bravo, Aniss. Tu as fait du bon travail. Aniss a choisi la fenêtre, le dessin, et le lion Sami. Le lion Sami ferme un œil de bouton. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16013,7 +17201,13 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis j'ai parlé.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss a choisi la fenêtre, le dessin, et le lion Sami.
+narrateur|Le lion Sami ferme un œil de bouton.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16035,7 +17229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16129,6 +17323,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-026.xlsx
+++ b/stories/arbres/TREE-COL-026.xlsx
@@ -854,7 +854,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Un cerf-volant rouge s'accroche au figuier. Aniss veut le copier sur l'ardoise verte avant le vent. Sa première phrase se perd, la craie casse, sa main se couvre de poussière. Sur le tapis, la table ou la fenêtre, il apprend à attendre la fin des voix. L'éponge, la craie ou le tabouret changent le dessin. Le clou, le pain ou le volet lui donnent enfin des oreilles. Le soir, l'ardoise garde le cerf-volant, et sa main n'est plus trop pressée.</t>
+          <t>Un cerf-volant rouge s'accroche au figuier. Aniss veut le copier sur l'ardoise verte avant le vent. Sa première phrase se perd, la craie casse, sa main se couvre de poussière. Sur le tapis, la table ou la fenêtre, il attend la fin des voix. L'éponge, la craie ou le tabouret changent le dessin. Le clou, le pain ou le volet lui donnent enfin des oreilles. Le soir, l'ardoise garde le cerf-volant, et sa main n'est plus trop pressée.</t>
         </is>
       </c>
     </row>
@@ -2933,17 +2933,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le clou. On a entendu toute ta phrase. Sa paume est propre, un peu froide. Une goutte tombe du clou, sur la laine grise.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le clou. Tes mots sont arrivés, cette fois. Sa paume est propre, un peu froide. Une goutte tombe du clou, sur la laine grise.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le clou. On a entendu toute ta phrase. Sa paume est propre, un peu froide. Une goutte tombe du clou, sur la laine grise.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le clou. Tes mots sont arrivés, cette fois. Sa paume est propre, un peu froide. Une goutte tombe du clou, sur la laine grise.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le clou. On a entendu toute ta phrase. Sa paume est propre, un peu froide. Une goutte tombe du clou, sur la laine grise.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le clou. Tes mots sont arrivés, cette fois. Sa paume est propre, un peu froide. Une goutte tombe du clou, sur la laine grise.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -3081,7 +3081,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur le tapis, avec l'éponge, puis le clou.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa paume est propre, un peu froide.
 narrateur|Une goutte tombe du clou, sur la laine grise.</t>
         </is>
@@ -3303,17 +3303,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le pain. On a entendu toute ta phrase. Sa paume est propre, un peu froide. L'éponge humide garde une miette de pain.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le pain. Tes mots sont arrivés, cette fois. Sa paume est propre, un peu froide. L'éponge humide garde une miette de pain.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le pain. On a entendu toute ta phrase. Sa paume est propre, un peu froide. L'éponge humide garde une miette de pain.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le pain. Tes mots sont arrivés, cette fois. Sa paume est propre, un peu froide. L'éponge humide garde une miette de pain.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le pain. On a entendu toute ta phrase. Sa paume est propre, un peu froide. L'éponge humide garde une miette de pain.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le pain. Tes mots sont arrivés, cette fois. Sa paume est propre, un peu froide. L'éponge humide garde une miette de pain.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -3451,7 +3451,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur le tapis, avec l'éponge, puis le pain.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa paume est propre, un peu froide.
 narrateur|L'éponge humide garde une miette de pain.</t>
         </is>
@@ -3673,17 +3673,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le volet. On a entendu toute ta phrase. Sa paume est propre, un peu froide. Sur le tapis, l'éponge sèche près du volet ouvert.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le volet. Tes mots sont arrivés, cette fois. Sa paume est propre, un peu froide. Sur le tapis, l'éponge sèche près du volet ouvert.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le volet. On a entendu toute ta phrase. Sa paume est propre, un peu froide. Sur le tapis, l'éponge sèche près du volet ouvert.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le volet. Tes mots sont arrivés, cette fois. Sa paume est propre, un peu froide. Sur le tapis, l'éponge sèche près du volet ouvert.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le volet. On a entendu toute ta phrase. Sa paume est propre, un peu froide. Sur le tapis, l'éponge sèche près du volet ouvert.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec l'éponge, puis le volet. Tes mots sont arrivés, cette fois. Sa paume est propre, un peu froide. Sur le tapis, l'éponge sèche près du volet ouvert.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -3821,7 +3821,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur le tapis, avec l'éponge, puis le volet.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa paume est propre, un peu froide.
 narrateur|Sur le tapis, l'éponge sèche près du volet ouvert.</t>
         </is>
@@ -4433,17 +4433,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le clou. On a entendu toute ta phrase. Un croissant jaune reste au creux de sa main. Un grain de craie jaune dort sous le clou.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le clou. Tes mots sont arrivés, cette fois. Un croissant jaune reste au creux de sa main. Un grain de craie jaune dort sous le clou.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le clou. On a entendu toute ta phrase. Un croissant jaune reste au creux de sa main. Un grain de craie jaune dort sous le clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le clou. Tes mots sont arrivés, cette fois. Un croissant jaune reste au creux de sa main. Un grain de craie jaune dort sous le clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le clou. On a entendu toute ta phrase. Un croissant jaune reste au creux de sa main. Un grain de craie jaune dort sous le clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le clou. Tes mots sont arrivés, cette fois. Un croissant jaune reste au creux de sa main. Un grain de craie jaune dort sous le clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -4581,7 +4581,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur le tapis, avec la craie neuve, puis le clou.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Un croissant jaune reste au creux de sa main.
 narrateur|Un grain de craie jaune dort sous le clou.</t>
         </is>
@@ -4615,17 +4615,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Aniss pose l'ardoise à côté de la croûte. La craie jaune roule vers le pain. Attention, ma ligne ! Maman rit d'une phrase de papa. Personne n'a vu la craie. Aniss la rattrape, puis il attend. Pardon, on était loin. Montre ton trait. Le jaune, c'est le soleil sur le rouge. On croirait le figuier, en miniature. Farine et craie se touchent, sur sa main. Deux blancs différents, l'un chaud, l'un sec. Le pain peut veiller le dessin.</t>
+          <t>Aniss pose l'ardoise à côté de la croûte. La craie jaune roule vers le pain. Attention, ma ligne ! Maman rit d'une phrase de papa. Personne n'a vu la craie. Aniss la rattrape, puis il attend. Pardon, on était loin. Montre ton trait. Le jaune, c'est le soleil sur le rouge. On dirait le figuier, plus petit. Farine et craie se touchent, sur sa main. Deux blancs différents, l'un chaud, l'un sec. Le pain peut veiller le dessin.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss pose l'ardoise à côté de la croûte. La craie jaune roule vers le pain. Attention, ma ligne ! Maman rit d'une phrase de papa. Personne n'a vu la craie. Aniss la rattrape, puis il attend. Pardon, on était loin. Montre ton trait. Le jaune, c'est le soleil sur le rouge. On croirait le figuier, en miniature. Farine et craie se touchent, sur sa main. Deux blancs différents, l'un chaud, l'un sec. Le pain peut veiller le dessin.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss pose l'ardoise à côté de la croûte. La craie jaune roule vers le pain. Attention, ma ligne ! Maman rit d'une phrase de papa. Personne n'a vu la craie. Aniss la rattrape, puis il attend. Pardon, on était loin. Montre ton trait. Le jaune, c'est le soleil sur le rouge. On dirait le figuier, plus petit. Farine et craie se touchent, sur sa main. Deux blancs différents, l'un chaud, l'un sec. Le pain peut veiller le dessin.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Aniss pose l'ardoise à côté de la croûte. La craie jaune roule vers le pain. Attention, ma ligne ! Maman rit d'une phrase de papa. Personne n'a vu la craie. Aniss la rattrape, puis il attend. Pardon, on était loin. Montre ton trait. Le jaune, c'est le soleil sur le rouge. On croirait le figuier, en miniature. Farine et craie se touchent, sur sa main. Deux blancs différents, l'un chaud, l'un sec. Le pain peut veiller le dessin. [pause]</t>
+          <t>Aniss pose l'ardoise à côté de la croûte. La craie jaune roule vers le pain. Attention, ma ligne ! Maman rit d'une phrase de papa. Personne n'a vu la craie. Aniss la rattrape, puis il attend. Pardon, on était loin. Montre ton trait. Le jaune, c'est le soleil sur le rouge. On dirait le figuier, plus petit. Farine et craie se touchent, sur sa main. Deux blancs différents, l'un chaud, l'un sec. Le pain peut veiller le dessin. [pause]</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4768,7 +4768,7 @@
 maman|Pardon, on était loin.
 maman|Montre ton trait.
 enfant-m|Le jaune, c'est le soleil sur le rouge.
-papa|On croirait le figuier, en miniature.
+papa|On dirait le figuier, plus petit.
 narrateur|Farine et craie se touchent, sur sa main.
 narrateur|Deux blancs différents, l'un chaud, l'un sec.
 maman|Le pain peut veiller le dessin.</t>
@@ -4803,17 +4803,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le pain. On a entendu toute ta phrase. Un croissant jaune reste au creux de sa main. La croûte et la craie sentent le chaud, toutes les deux.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le pain. Tes mots sont arrivés, cette fois. Un croissant jaune reste au creux de sa main. La croûte et la craie sentent le chaud, toutes les deux.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le pain. On a entendu toute ta phrase. Un croissant jaune reste au creux de sa main. La croûte et la craie sentent le chaud, toutes les deux.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le pain. Tes mots sont arrivés, cette fois. Un croissant jaune reste au creux de sa main. La croûte et la craie sentent le chaud, toutes les deux.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le pain. On a entendu toute ta phrase. Un croissant jaune reste au creux de sa main. La croûte et la craie sentent le chaud, toutes les deux.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le pain. Tes mots sont arrivés, cette fois. Un croissant jaune reste au creux de sa main. La croûte et la craie sentent le chaud, toutes les deux.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -4951,7 +4951,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur le tapis, avec la craie neuve, puis le pain.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Un croissant jaune reste au creux de sa main.
 narrateur|La croûte et la craie sentent le chaud, toutes les deux.</t>
         </is>
@@ -4985,17 +4985,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Aniss lève l'ardoise vers le volet, craie au poing. Il veut finir la queue dehors. Un trait, juste un ! Le mot trop vite se perd dans le vent. Le volet bouge, le trait dérape. Aniss recule d'un pas, sur le tapis. Il attend que le bois tienne. Le volet est calme. Finis ta queue. Voilà, elle rejoint la vraie. Dehors et dedans se saluent. La boîte ronde brille sur le rebord. Sa main jaune laisse une virgule au loquet.</t>
+          <t>Aniss lève l'ardoise vers le volet, craie au poing. Il veut finir la queue dehors. Un trait, juste un ! Sa phrase trop vite se perd dans le vent. Le volet bouge, le trait dérape. Aniss recule d'un pas, sur le tapis. Il attend que le bois tienne. Le volet est calme. Finis ta queue. Voilà, elle rejoint la vraie. Dehors et dedans se saluent. La boîte ronde brille sur le rebord. Sa main jaune laisse une virgule au loquet.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss lève l'ardoise vers le volet, craie au poing. Il veut finir la queue dehors. Un trait, juste un ! Le mot trop vite se perd dans le vent. Le volet bouge, le trait dérape. Aniss recule d'un pas, sur le tapis. Il attend que le bois tienne. Le volet est calme. Finis ta queue. Voilà, elle rejoint la vraie. Dehors et dedans se saluent. La boîte ronde brille sur le rebord. Sa main jaune laisse une virgule au loquet.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss lève l'ardoise vers le volet, craie au poing. Il veut finir la queue dehors. Un trait, juste un ! Sa phrase trop vite se perd dans le vent. Le volet bouge, le trait dérape. Aniss recule d'un pas, sur le tapis. Il attend que le bois tienne. Le volet est calme. Finis ta queue. Voilà, elle rejoint la vraie. Dehors et dedans se saluent. La boîte ronde brille sur le rebord. Sa main jaune laisse une virgule au loquet.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Aniss lève l'ardoise vers le volet, craie au poing. Il veut finir la queue dehors. Un trait, juste un ! Le mot trop vite se perd dans le vent. Le volet bouge, le trait dérape. Aniss recule d'un pas, sur le tapis. Il attend que le bois tienne. Le volet est calme. Finis ta queue. Voilà, elle rejoint la vraie. Dehors et dedans se saluent. La boîte ronde brille sur le rebord. Sa main jaune laisse une virgule au loquet. [pause]</t>
+          <t>Aniss lève l'ardoise vers le volet, craie au poing. Il veut finir la queue dehors. Un trait, juste un ! Sa phrase trop vite se perd dans le vent. Le volet bouge, le trait dérape. Aniss recule d'un pas, sur le tapis. Il attend que le bois tienne. Le volet est calme. Finis ta queue. Voilà, elle rejoint la vraie. Dehors et dedans se saluent. La boîte ronde brille sur le rebord. Sa main jaune laisse une virgule au loquet. [pause]</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
           <t>narrateur|Aniss lève l'ardoise vers le volet, craie au poing.
 narrateur|Il veut finir la queue dehors.
 enfant-m|Un trait, juste un !
-narrateur|Le mot trop vite se perd dans le vent.
+narrateur|Sa phrase trop vite se perd dans le vent.
 narrateur|Le volet bouge, le trait dérape.
 narrateur|Aniss recule d'un pas, sur le tapis.
 narrateur|Il attend que le bois tienne.
@@ -5173,17 +5173,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le volet. On a entendu toute ta phrase. Un croissant jaune reste au creux de sa main. La boîte ronde brille sur le rebord du volet.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le volet. Tes mots sont arrivés, cette fois. Un croissant jaune reste au creux de sa main. La boîte ronde brille sur le rebord du volet.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le volet. On a entendu toute ta phrase. Un croissant jaune reste au creux de sa main. La boîte ronde brille sur le rebord du volet.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le volet. Tes mots sont arrivés, cette fois. Un croissant jaune reste au creux de sa main. La boîte ronde brille sur le rebord du volet.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le volet. On a entendu toute ta phrase. Un croissant jaune reste au creux de sa main. La boîte ronde brille sur le rebord du volet.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec la craie neuve, puis le volet. Tes mots sont arrivés, cette fois. Un croissant jaune reste au creux de sa main. La boîte ronde brille sur le rebord du volet.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -5321,7 +5321,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur le tapis, avec la craie neuve, puis le volet.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Un croissant jaune reste au creux de sa main.
 narrateur|La boîte ronde brille sur le rebord du volet.</t>
         </is>
@@ -5745,17 +5745,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Du tabouret, le clou est juste à hauteur. Aniss tend l'ardoise, les talons levés. Je l'accroche ! Papa parle, et le tabouret penche. Aniss ravalé son cri. Il attend que papa tienne le bois. Je te tiens. Vas-y, doucement. L'ardoise trouve le clou, sans choc. Il est plus grand que le tabouret. On le voit depuis le tapis. Le tabouret vide regarde trop haut. Sa main quitte le rebord, un peu fière.</t>
+          <t>Du tabouret, le clou est juste à hauteur. Aniss tend l'ardoise, les talons levés. Je l'accroche ! Papa parle, et le tabouret penche. Aniss ravale son cri. Il attend que papa tienne le bois. Je te tiens. Vas-y, doucement. L'ardoise trouve le clou, sans choc. Il est plus grand que le tabouret. On le voit depuis le tapis. Le tabouret vide regarde trop haut. Sa main quitte le rebord, un peu fière.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Du tabouret, le clou est juste à hauteur. Aniss tend l'ardoise, les talons levés. Je l'accroche ! Papa parle, et le tabouret penche. Aniss ravalé son cri. Il attend que papa tienne le bois. Je te tiens. Vas-y, doucement. L'ardoise trouve le clou, sans choc. Il est plus grand que le tabouret. On le voit depuis le tapis. Le tabouret vide regarde trop haut. Sa main quitte le rebord, un peu fière.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Du tabouret, le clou est juste à hauteur. Aniss tend l'ardoise, les talons levés. Je l'accroche ! Papa parle, et le tabouret penche. Aniss ravale son cri. Il attend que papa tienne le bois. Je te tiens. Vas-y, doucement. L'ardoise trouve le clou, sans choc. Il est plus grand que le tabouret. On le voit depuis le tapis. Le tabouret vide regarde trop haut. Sa main quitte le rebord, un peu fière.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Du tabouret, le clou est juste à hauteur. Aniss tend l'ardoise, les talons levés. Je l'accroche ! Papa parle, et le tabouret penche. Aniss ravalé son cri. Il attend que papa tienne le bois. Je te tiens. Vas-y, doucement. L'ardoise trouve le clou, sans choc. Il est plus grand que le tabouret. On le voit depuis le tapis. Le tabouret vide regarde trop haut. Sa main quitte le rebord, un peu fière. [pause]</t>
+          <t>Du tabouret, le clou est juste à hauteur. Aniss tend l'ardoise, les talons levés. Je l'accroche ! Papa parle, et le tabouret penche. Aniss ravale son cri. Il attend que papa tienne le bois. Je te tiens. Vas-y, doucement. L'ardoise trouve le clou, sans choc. Il est plus grand que le tabouret. On le voit depuis le tapis. Le tabouret vide regarde trop haut. Sa main quitte le rebord, un peu fière. [pause]</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -5893,7 +5893,7 @@
 narrateur|Aniss tend l'ardoise, les talons levés.
 enfant-m|Je l'accroche !
 narrateur|Papa parle, et le tabouret penche.
-narrateur|Aniss ravalé son cri.
+narrateur|Aniss ravale son cri.
 narrateur|Il attend que papa tienne le bois.
 papa|Je te tiens.
 papa|Vas-y, doucement.
@@ -5933,17 +5933,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le clou. On a entendu toute ta phrase. Sa main sent le bois du tabouret. Le tabouret vide regarde l'ardoise, trop haute pour lui.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le clou. Tes mots sont arrivés, cette fois. Sa main sent le bois du tabouret. Le tabouret vide regarde l'ardoise, trop haute pour lui.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le clou. On a entendu toute ta phrase. Sa main sent le bois du tabouret. Le tabouret vide regarde l'ardoise, trop haute pour lui.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le clou. Tes mots sont arrivés, cette fois. Sa main sent le bois du tabouret. Le tabouret vide regarde l'ardoise, trop haute pour lui.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le clou. On a entendu toute ta phrase. Sa main sent le bois du tabouret. Le tabouret vide regarde l'ardoise, trop haute pour lui.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le clou. Tes mots sont arrivés, cette fois. Sa main sent le bois du tabouret. Le tabouret vide regarde l'ardoise, trop haute pour lui.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -6081,7 +6081,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur le tapis, avec le tabouret, puis le clou.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa main sent le bois du tabouret.
 narrateur|Le tabouret vide regarde l'ardoise, trop haute pour lui.</t>
         </is>
@@ -6303,17 +6303,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le pain. On a entendu toute ta phrase. Sa main sent le bois du tabouret. Aniss redescend ; le pain et l'ardoise partagent le soleil.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le pain. Tes mots sont arrivés, cette fois. Sa main sent le bois du tabouret. Aniss redescend ; le pain et l'ardoise partagent le soleil.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le pain. On a entendu toute ta phrase. Sa main sent le bois du tabouret. Aniss redescend ; le pain et l'ardoise partagent le soleil.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le pain. Tes mots sont arrivés, cette fois. Sa main sent le bois du tabouret. Aniss redescend ; le pain et l'ardoise partagent le soleil.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le pain. On a entendu toute ta phrase. Sa main sent le bois du tabouret. Aniss redescend ; le pain et l'ardoise partagent le soleil.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le pain. Tes mots sont arrivés, cette fois. Sa main sent le bois du tabouret. Aniss redescend ; le pain et l'ardoise partagent le soleil.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur le tapis, avec le tabouret, puis le pain.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa main sent le bois du tabouret.
 narrateur|Aniss redescend ; le pain et l'ardoise partagent le soleil.</t>
         </is>
@@ -6485,17 +6485,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Aniss, sur le tabouret, attrape le volet. Il veut coller l'ardoise au bois. Regarde, c'est le même ! Le vent répond à sa place. Le volet frappe, presque. Aniss se tait, une main sur le loquet. Je retiens le bois. Parle, maintenant. Dehors il danse, ici il tient. Deux danses, une seule histoire de queue. Sa main haute garde le volet. Le tabouret ne bouge plus. Un fil de laine s'accroche à son talon.</t>
+          <t>Aniss, sur le tabouret, attrape le volet. Il veut coller l'ardoise au bois. Regarde, c'est le même ! Le vent répond à sa place. Le volet frappe, presque. Aniss se tait, une main sur le loquet. Je retiens le bois. Parle, maintenant. Dehors il danse, ici il tient. Deux danses, et une seule queue. Sa main haute garde le volet. Le tabouret ne bouge plus. Un fil de laine s'accroche à son talon.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss, sur le tabouret, attrape le volet. Il veut coller l'ardoise au bois. Regarde, c'est le même ! Le vent répond à sa place. Le volet frappe, presque. Aniss se tait, une main sur le loquet. Je retiens le bois. Parle, maintenant. Dehors il danse, ici il tient. Deux danses, une seule histoire de queue. Sa main haute garde le volet. Le tabouret ne bouge plus. Un fil de laine s'accroche à son talon.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss, sur le tabouret, attrape le volet. Il veut coller l'ardoise au bois. Regarde, c'est le même ! Le vent répond à sa place. Le volet frappe, presque. Aniss se tait, une main sur le loquet. Je retiens le bois. Parle, maintenant. Dehors il danse, ici il tient. Deux danses, et une seule queue. Sa main haute garde le volet. Le tabouret ne bouge plus. Un fil de laine s'accroche à son talon.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Aniss, sur le tabouret, attrape le volet. Il veut coller l'ardoise au bois. Regarde, c'est le même ! Le vent répond à sa place. Le volet frappe, presque. Aniss se tait, une main sur le loquet. Je retiens le bois. Parle, maintenant. Dehors il danse, ici il tient. Deux danses, une seule histoire de queue. Sa main haute garde le volet. Le tabouret ne bouge plus. Un fil de laine s'accroche à son talon. [pause]</t>
+          <t>Aniss, sur le tabouret, attrape le volet. Il veut coller l'ardoise au bois. Regarde, c'est le même ! Le vent répond à sa place. Le volet frappe, presque. Aniss se tait, une main sur le loquet. Je retiens le bois. Parle, maintenant. Dehors il danse, ici il tient. Deux danses, et une seule queue. Sa main haute garde le volet. Le tabouret ne bouge plus. Un fil de laine s'accroche à son talon. [pause]</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6638,7 +6638,7 @@
 papa|Je retiens le bois.
 papa|Parle, maintenant.
 enfant-m|Dehors il danse, ici il tient.
-maman|Deux danses, une seule histoire de queue.
+maman|Deux danses, et une seule queue.
 narrateur|Sa main haute garde le volet.
 narrateur|Le tabouret ne bouge plus.
 narrateur|Un fil de laine s'accroche à son talon.</t>
@@ -6673,17 +6673,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le volet. On a entendu toute ta phrase. Sa main sent le bois du tabouret. Sa main tient le volet, sans bouger, là-haut.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le volet. Tes mots sont arrivés, cette fois. Sa main sent le bois du tabouret. Sa main tient le volet, sans bouger, là-haut.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le volet. On a entendu toute ta phrase. Sa main sent le bois du tabouret. Sa main tient le volet, sans bouger, là-haut.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le volet. Tes mots sont arrivés, cette fois. Sa main sent le bois du tabouret. Sa main tient le volet, sans bouger, là-haut.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le volet. On a entendu toute ta phrase. Sa main sent le bois du tabouret. Sa main tient le volet, sans bouger, là-haut.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur le tapis, avec le tabouret, puis le volet. Tes mots sont arrivés, cette fois. Sa main sent le bois du tabouret. Sa main tient le volet, sans bouger, là-haut.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -6821,7 +6821,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur le tapis, avec le tabouret, puis le volet.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa main sent le bois du tabouret.
 narrateur|Sa main tient le volet, sans bouger, là-haut.</t>
         </is>
@@ -8190,17 +8190,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le clou. On a entendu toute ta phrase. Ses doigts sentent l'eau et la farine. Des miettes collent au bord mouillé de l'ardoise.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le clou. Tes mots sont arrivés, cette fois. Ses doigts sentent l'eau et la farine. Des miettes collent au bord mouillé de l'ardoise.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le clou. On a entendu toute ta phrase. Ses doigts sentent l'eau et la farine. Des miettes collent au bord mouillé de l'ardoise.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le clou. Tes mots sont arrivés, cette fois. Ses doigts sentent l'eau et la farine. Des miettes collent au bord mouillé de l'ardoise.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le clou. On a entendu toute ta phrase. Ses doigts sentent l'eau et la farine. Des miettes collent au bord mouillé de l'ardoise.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le clou. Tes mots sont arrivés, cette fois. Ses doigts sentent l'eau et la farine. Des miettes collent au bord mouillé de l'ardoise.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -8338,7 +8338,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur la table, avec l'éponge, puis le clou.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Ses doigts sentent l'eau et la farine.
 narrateur|Des miettes collent au bord mouillé de l'ardoise.</t>
         </is>
@@ -8560,17 +8560,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le pain. On a entendu toute ta phrase. Ses doigts sentent l'eau et la farine. Le couteau repose ; le cerf-volant pâle sèche au pain.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le pain. Tes mots sont arrivés, cette fois. Ses doigts sentent l'eau et la farine. Le couteau repose ; le cerf-volant pâle sèche au pain.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le pain. On a entendu toute ta phrase. Ses doigts sentent l'eau et la farine. Le couteau repose ; le cerf-volant pâle sèche au pain.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le pain. Tes mots sont arrivés, cette fois. Ses doigts sentent l'eau et la farine. Le couteau repose ; le cerf-volant pâle sèche au pain.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le pain. On a entendu toute ta phrase. Ses doigts sentent l'eau et la farine. Le couteau repose ; le cerf-volant pâle sèche au pain.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le pain. Tes mots sont arrivés, cette fois. Ses doigts sentent l'eau et la farine. Le couteau repose ; le cerf-volant pâle sèche au pain.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -8708,7 +8708,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur la table, avec l'éponge, puis le pain.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Ses doigts sentent l'eau et la farine.
 narrateur|Le couteau repose ; le cerf-volant pâle sèche au pain.</t>
         </is>
@@ -8742,17 +8742,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Aniss pousse l'ardoise mouillée vers le volet. Une goutte court sur la table, vers les pièces. Vite, le vrai est là ! Les pièces tintent, papa répond. La goutte s'arrête contre une pièce. Aniss retient sa phrase. Les pièces sont sages. Ouvre le volet, on compare. Pâle ici, rouge là-bas. Deux versions, une même queue. L'éponge laisse un rond sur le bois. Sa main écarte le volet, sans claquer. Le figuier entre dans la cuisine.</t>
+          <t>Aniss pousse l'ardoise mouillée vers le volet. Une goutte court sur la table, vers les pièces. Vite, le vrai est là ! Les pièces tintent, papa répond. La goutte s'arrête contre une pièce. Aniss retient sa phrase. Les pièces sont sages. Ouvre le volet, on compare. Pâle ici, rouge là-bas. Deux queues, une pâle, une rouge. L'éponge laisse un rond sur le bois. Sa main écarte le volet, sans claquer. Le figuier entre dans la cuisine.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss pousse l'ardoise mouillée vers le volet. Une goutte court sur la table, vers les pièces. Vite, le vrai est là ! Les pièces tintent, papa répond. La goutte s'arrête contre une pièce. Aniss retient sa phrase. Les pièces sont sages. Ouvre le volet, on compare. Pâle ici, rouge là-bas. Deux versions, une même queue. L'éponge laisse un rond sur le bois. Sa main écarte le volet, sans claquer. Le figuier entre dans la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss pousse l'ardoise mouillée vers le volet. Une goutte court sur la table, vers les pièces. Vite, le vrai est là ! Les pièces tintent, papa répond. La goutte s'arrête contre une pièce. Aniss retient sa phrase. Les pièces sont sages. Ouvre le volet, on compare. Pâle ici, rouge là-bas. Deux queues, une pâle, une rouge. L'éponge laisse un rond sur le bois. Sa main écarte le volet, sans claquer. Le figuier entre dans la cuisine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Aniss pousse l'ardoise mouillée vers le volet. Une goutte court sur la table, vers les pièces. Vite, le vrai est là ! Les pièces tintent, papa répond. La goutte s'arrête contre une pièce. Aniss retient sa phrase. Les pièces sont sages. Ouvre le volet, on compare. Pâle ici, rouge là-bas. Deux versions, une même queue. L'éponge laisse un rond sur le bois. Sa main écarte le volet, sans claquer. Le figuier entre dans la cuisine. [pause]</t>
+          <t>Aniss pousse l'ardoise mouillée vers le volet. Une goutte court sur la table, vers les pièces. Vite, le vrai est là ! Les pièces tintent, papa répond. La goutte s'arrête contre une pièce. Aniss retient sa phrase. Les pièces sont sages. Ouvre le volet, on compare. Pâle ici, rouge là-bas. Deux queues, une pâle, une rouge. L'éponge laisse un rond sur le bois. Sa main écarte le volet, sans claquer. Le figuier entre dans la cuisine. [pause]</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -8895,7 +8895,7 @@
 papa|Les pièces sont sages.
 papa|Ouvre le volet, on compare.
 enfant-m|Pâle ici, rouge là-bas.
-maman|Deux versions, une même queue.
+maman|Deux queues, une pâle, une rouge.
 narrateur|L'éponge laisse un rond sur le bois.
 narrateur|Sa main écarte le volet, sans claquer.
 narrateur|Le figuier entre dans la cuisine.</t>
@@ -8930,17 +8930,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le volet. On a entendu toute ta phrase. Ses doigts sentent l'eau et la farine. Une goutte court vers les pièces, puis s'arrête.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le volet. Tes mots sont arrivés, cette fois. Ses doigts sentent l'eau et la farine. Une goutte court vers les pièces, puis s'arrête.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le volet. On a entendu toute ta phrase. Ses doigts sentent l'eau et la farine. Une goutte court vers les pièces, puis s'arrête.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le volet. Tes mots sont arrivés, cette fois. Ses doigts sentent l'eau et la farine. Une goutte court vers les pièces, puis s'arrête.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le volet. On a entendu toute ta phrase. Ses doigts sentent l'eau et la farine. Une goutte court vers les pièces, puis s'arrête.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec l'éponge, puis le volet. Tes mots sont arrivés, cette fois. Ses doigts sentent l'eau et la farine. Une goutte court vers les pièces, puis s'arrête.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -9078,7 +9078,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur la table, avec l'éponge, puis le volet.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Ses doigts sentent l'eau et la farine.
 narrateur|Une goutte court vers les pièces, puis s'arrête.</t>
         </is>
@@ -9690,17 +9690,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le clou. On a entendu toute ta phrase. Deux poudres blanches ornent ses ongles. La boîte ronde garde le pied du clou.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le clou. Tes mots sont arrivés, cette fois. Deux poudres blanches ornent ses ongles. La boîte ronde garde le pied du clou.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le clou. On a entendu toute ta phrase. Deux poudres blanches ornent ses ongles. La boîte ronde garde le pied du clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le clou. Tes mots sont arrivés, cette fois. Deux poudres blanches ornent ses ongles. La boîte ronde garde le pied du clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le clou. On a entendu toute ta phrase. Deux poudres blanches ornent ses ongles. La boîte ronde garde le pied du clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le clou. Tes mots sont arrivés, cette fois. Deux poudres blanches ornent ses ongles. La boîte ronde garde le pied du clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -9838,7 +9838,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur la table, avec la craie neuve, puis le clou.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Deux poudres blanches ornent ses ongles.
 narrateur|La boîte ronde garde le pied du clou.</t>
         </is>
@@ -10060,17 +10060,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le pain. On a entendu toute ta phrase. Deux poudres blanches ornent ses ongles. Farine et craie se mêlent au bout de ses doigts.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le pain. Tes mots sont arrivés, cette fois. Deux poudres blanches ornent ses ongles. Farine et craie se mêlent au bout de ses doigts.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le pain. On a entendu toute ta phrase. Deux poudres blanches ornent ses ongles. Farine et craie se mêlent au bout de ses doigts.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le pain. Tes mots sont arrivés, cette fois. Deux poudres blanches ornent ses ongles. Farine et craie se mêlent au bout de ses doigts.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le pain. On a entendu toute ta phrase. Deux poudres blanches ornent ses ongles. Farine et craie se mêlent au bout de ses doigts.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le pain. Tes mots sont arrivés, cette fois. Deux poudres blanches ornent ses ongles. Farine et craie se mêlent au bout de ses doigts.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -10208,7 +10208,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur la table, avec la craie neuve, puis le pain.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Deux poudres blanches ornent ses ongles.
 narrateur|Farine et craie se mêlent au bout de ses doigts.</t>
         </is>
@@ -10242,17 +10242,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Aniss porte craie et ardoise vers le volet. Il veut la dernière ligne pendant que papa parle. La nervure de la feuille ! Le volet cède d'un souffle. La ligne part de travers. Aniss pose la craie, les lèvres closes. Je tiens le volet. Recommence la nervure. Voilà, elle rejoint le figuier. Le volet dort, la ligne est nette. Un grain jaune reste au loquet. Sa main ne cache plus le dessin. Dehors, le rouge approuve, sans un mot.</t>
+          <t>Aniss porte craie et ardoise vers le volet. Il veut la dernière ligne pendant que papa parle. Le trait de la feuille ! Le volet cède d'un souffle. La ligne part de travers. Aniss pose la craie, les lèvres closes. Je tiens le volet. Recommence le trait de feuille. Voilà, elle rejoint le figuier. Le volet dort, la ligne est nette. Un grain jaune reste au loquet. Sa main ne cache plus le dessin. Dehors, le rouge approuve, sans un mot.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss porte craie et ardoise vers le volet. Il veut la dernière ligne pendant que papa parle. La nervure de la feuille ! Le volet cède d'un souffle. La ligne part de travers. Aniss pose la craie, les lèvres closes. Je tiens le volet. Recommence la nervure. Voilà, elle rejoint le figuier. Le volet dort, la ligne est nette. Un grain jaune reste au loquet. Sa main ne cache plus le dessin. Dehors, le rouge approuve, sans un mot.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss porte craie et ardoise vers le volet. Il veut la dernière ligne pendant que papa parle. Le trait de la feuille ! Le volet cède d'un souffle. La ligne part de travers. Aniss pose la craie, les lèvres closes. Je tiens le volet. Recommence le trait de feuille. Voilà, elle rejoint le figuier. Le volet dort, la ligne est nette. Un grain jaune reste au loquet. Sa main ne cache plus le dessin. Dehors, le rouge approuve, sans un mot.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Aniss porte craie et ardoise vers le volet. Il veut la dernière ligne pendant que papa parle. La nervure de la feuille ! Le volet cède d'un souffle. La ligne part de travers. Aniss pose la craie, les lèvres closes. Je tiens le volet. Recommence la nervure. Voilà, elle rejoint le figuier. Le volet dort, la ligne est nette. Un grain jaune reste au loquet. Sa main ne cache plus le dessin. Dehors, le rouge approuve, sans un mot. [pause]</t>
+          <t>Aniss porte craie et ardoise vers le volet. Il veut la dernière ligne pendant que papa parle. Le trait de la feuille ! Le volet cède d'un souffle. La ligne part de travers. Aniss pose la craie, les lèvres closes. Je tiens le volet. Recommence le trait de feuille. Voilà, elle rejoint le figuier. Le volet dort, la ligne est nette. Un grain jaune reste au loquet. Sa main ne cache plus le dessin. Dehors, le rouge approuve, sans un mot. [pause]</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -10388,12 +10388,12 @@
         <is>
           <t>narrateur|Aniss porte craie et ardoise vers le volet.
 narrateur|Il veut la dernière ligne pendant que papa parle.
-enfant-m|La nervure de la feuille !
+enfant-m|Le trait de la feuille !
 narrateur|Le volet cède d'un souffle.
 narrateur|La ligne part de travers.
 narrateur|Aniss pose la craie, les lèvres closes.
 papa|Je tiens le volet.
-papa|Recommence la nervure.
+papa|Recommence le trait de feuille.
 enfant-m|Voilà, elle rejoint le figuier.
 maman|Le volet dort, la ligne est nette.
 narrateur|Un grain jaune reste au loquet.
@@ -10430,17 +10430,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le volet. On a entendu toute ta phrase. Deux poudres blanches ornent ses ongles. Le volet dort ; la dernière ligne est nette.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le volet. Tes mots sont arrivés, cette fois. Deux poudres blanches ornent ses ongles. Le volet dort ; la dernière ligne est nette.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le volet. On a entendu toute ta phrase. Deux poudres blanches ornent ses ongles. Le volet dort ; la dernière ligne est nette.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le volet. Tes mots sont arrivés, cette fois. Deux poudres blanches ornent ses ongles. Le volet dort ; la dernière ligne est nette.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le volet. On a entendu toute ta phrase. Deux poudres blanches ornent ses ongles. Le volet dort ; la dernière ligne est nette.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec la craie neuve, puis le volet. Tes mots sont arrivés, cette fois. Deux poudres blanches ornent ses ongles. Le volet dort ; la dernière ligne est nette.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -10578,7 +10578,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur la table, avec la craie neuve, puis le volet.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Deux poudres blanches ornent ses ongles.
 narrateur|Le volet dort ; la dernière ligne est nette.</t>
         </is>
@@ -11002,17 +11002,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Aniss pousse le tabouret sous le clou. La table recule d'un doigt. Je le mets en haut ! Une cuillère tombe, et papa s'exclame. Les mots d'Aniss se cassent. Il attend que la cuillère se taise. C'est bon, j'ai ramassé. Monte. L'ardoise gagne le clou, au-dessus du pain. Il surveille la table. Le tabouret rentre, l'ardoise veille. Sa main quitte le bois, un peu blanche. Une miette orpheline reste sur une barre.</t>
+          <t>Aniss pousse le tabouret sous le clou. La table recule d'un doigt. Je le mets en haut ! Une cuillère tombe, et papa s'exclame. Les mots d'Aniss se cassent. Il attend que la cuillère se taise. C'est bon, j'ai ramassé. Monte. L'ardoise gagne le clou, au-dessus du pain. Il surveille la table. Le tabouret rentre, l'ardoise veille. Sa main quitte le bois, un peu blanche. Une miette oubliée reste sur une barre.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss pousse le tabouret sous le clou. La table recule d'un doigt. Je le mets en haut ! Une cuillère tombe, et papa s'exclame. Les mots d'Aniss se cassent. Il attend que la cuillère se taise. C'est bon, j'ai ramassé. Monte. L'ardoise gagne le clou, au-dessus du pain. Il surveille la table. Le tabouret rentre, l'ardoise veille. Sa main quitte le bois, un peu blanche. Une miette orpheline reste sur une barre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss pousse le tabouret sous le clou. La table recule d'un doigt. Je le mets en haut ! Une cuillère tombe, et papa s'exclame. Les mots d'Aniss se cassent. Il attend que la cuillère se taise. C'est bon, j'ai ramassé. Monte. L'ardoise gagne le clou, au-dessus du pain. Il surveille la table. Le tabouret rentre, l'ardoise veille. Sa main quitte le bois, un peu blanche. Une miette oubliée reste sur une barre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Aniss pousse le tabouret sous le clou. La table recule d'un doigt. Je le mets en haut ! Une cuillère tombe, et papa s'exclame. Les mots d'Aniss se cassent. Il attend que la cuillère se taise. C'est bon, j'ai ramassé. Monte. L'ardoise gagne le clou, au-dessus du pain. Il surveille la table. Le tabouret rentre, l'ardoise veille. Sa main quitte le bois, un peu blanche. Une miette orpheline reste sur une barre. [pause]</t>
+          <t>Aniss pousse le tabouret sous le clou. La table recule d'un doigt. Je le mets en haut ! Une cuillère tombe, et papa s'exclame. Les mots d'Aniss se cassent. Il attend que la cuillère se taise. C'est bon, j'ai ramassé. Monte. L'ardoise gagne le clou, au-dessus du pain. Il surveille la table. Le tabouret rentre, l'ardoise veille. Sa main quitte le bois, un peu blanche. Une miette oubliée reste sur une barre. [pause]</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -11158,7 +11158,7 @@
 enfant-m|Il surveille la table.
 maman|Le tabouret rentre, l'ardoise veille.
 narrateur|Sa main quitte le bois, un peu blanche.
-narrateur|Une miette orpheline reste sur une barre.</t>
+narrateur|Une miette oubliée reste sur une barre.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -11190,17 +11190,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le clou. On a entendu toute ta phrase. Sa main a gardé la chaleur de la nappe. Le tabouret rentre sous la table ; l'ardoise veille.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le clou. Tes mots sont arrivés, cette fois. Sa main a gardé la chaleur de la nappe. Le tabouret rentre sous la table ; l'ardoise veille.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le clou. On a entendu toute ta phrase. Sa main a gardé la chaleur de la nappe. Le tabouret rentre sous la table ; l'ardoise veille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le clou. Tes mots sont arrivés, cette fois. Sa main a gardé la chaleur de la nappe. Le tabouret rentre sous la table ; l'ardoise veille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le clou. On a entendu toute ta phrase. Sa main a gardé la chaleur de la nappe. Le tabouret rentre sous la table ; l'ardoise veille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le clou. Tes mots sont arrivés, cette fois. Sa main a gardé la chaleur de la nappe. Le tabouret rentre sous la table ; l'ardoise veille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -11338,7 +11338,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur la table, avec le tabouret, puis le clou.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa main a gardé la chaleur de la nappe.
 narrateur|Le tabouret rentre sous la table ; l'ardoise veille.</t>
         </is>
@@ -11560,17 +11560,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le pain. On a entendu toute ta phrase. Sa main a gardé la chaleur de la nappe. Le cerf-volant de craie fait face à la miche.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le pain. Tes mots sont arrivés, cette fois. Sa main a gardé la chaleur de la nappe. Le cerf-volant de craie fait face à la miche.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le pain. On a entendu toute ta phrase. Sa main a gardé la chaleur de la nappe. Le cerf-volant de craie fait face à la miche.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le pain. Tes mots sont arrivés, cette fois. Sa main a gardé la chaleur de la nappe. Le cerf-volant de craie fait face à la miche.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le pain. On a entendu toute ta phrase. Sa main a gardé la chaleur de la nappe. Le cerf-volant de craie fait face à la miche.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le pain. Tes mots sont arrivés, cette fois. Sa main a gardé la chaleur de la nappe. Le cerf-volant de craie fait face à la miche.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -11708,7 +11708,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur la table, avec le tabouret, puis le pain.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa main a gardé la chaleur de la nappe.
 narrateur|Le cerf-volant de craie fait face à la miche.</t>
         </is>
@@ -11742,17 +11742,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Aniss hisse le tabouret contre le volet. Du haut, le figuier remplit la vitre. Il est énorme ! Papa veut fermer un peu, à cause du soleil. Leurs envies se croisent. Aniss pose l'ardoise, et il attend. On laisse ouvert ? Oui, pour copier la grande queue. Alors on compare, sans bouger le bois. Le cerf-volant de craie salue le vrai. Du tabouret, la place entière tient dans un cadre. Sa main ombre un coin de l'ardoise. On voit tout, grâce à toi.</t>
+          <t>Aniss pousse le tabouret contre le volet. Du haut, le figuier remplit la vitre. Il est énorme ! Papa veut fermer un peu, à cause du soleil. Leurs envies se croisent. Aniss pose l'ardoise, et il attend. On laisse ouvert ? Oui, pour copier la grande queue. Alors on compare, sans bouger le bois. Le cerf-volant de craie salue le vrai. Du tabouret, la place entière tient dans un cadre. Sa main ombre un coin de l'ardoise. On voit tout, grâce à toi.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss hisse le tabouret contre le volet. Du haut, le figuier remplit la vitre. Il est énorme ! Papa veut fermer un peu, à cause du soleil. Leurs envies se croisent. Aniss pose l'ardoise, et il attend. On laisse ouvert ? Oui, pour copier la grande queue. Alors on compare, sans bouger le bois. Le cerf-volant de craie salue le vrai. Du tabouret, la place entière tient dans un cadre. Sa main ombre un coin de l'ardoise. On voit tout, grâce à toi.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss pousse le tabouret contre le volet. Du haut, le figuier remplit la vitre. Il est énorme ! Papa veut fermer un peu, à cause du soleil. Leurs envies se croisent. Aniss pose l'ardoise, et il attend. On laisse ouvert ? Oui, pour copier la grande queue. Alors on compare, sans bouger le bois. Le cerf-volant de craie salue le vrai. Du tabouret, la place entière tient dans un cadre. Sa main ombre un coin de l'ardoise. On voit tout, grâce à toi.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Aniss hisse le tabouret contre le volet. Du haut, le figuier remplit la vitre. Il est énorme ! Papa veut fermer un peu, à cause du soleil. Leurs envies se croisent. Aniss pose l'ardoise, et il attend. On laisse ouvert ? Oui, pour copier la grande queue. Alors on compare, sans bouger le bois. Le cerf-volant de craie salue le vrai. Du tabouret, la place entière tient dans un cadre. Sa main ombre un coin de l'ardoise. On voit tout, grâce à toi. [pause]</t>
+          <t>Aniss pousse le tabouret contre le volet. Du haut, le figuier remplit la vitre. Il est énorme ! Papa veut fermer un peu, à cause du soleil. Leurs envies se croisent. Aniss pose l'ardoise, et il attend. On laisse ouvert ? Oui, pour copier la grande queue. Alors on compare, sans bouger le bois. Le cerf-volant de craie salue le vrai. Du tabouret, la place entière tient dans un cadre. Sa main ombre un coin de l'ardoise. On voit tout, grâce à toi. [pause]</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Aniss hisse le tabouret contre le volet.
+          <t>narrateur|Aniss pousse le tabouret contre le volet.
 narrateur|Du haut, le figuier remplit la vitre.
 enfant-m|Il est énorme !
 narrateur|Papa veut fermer un peu, à cause du soleil.
@@ -11930,17 +11930,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le volet. On a entendu toute ta phrase. Sa main a gardé la chaleur de la nappe. Du tabouret, le figuier remplit toute la vitre.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le volet. Tes mots sont arrivés, cette fois. Sa main a gardé la chaleur de la nappe. Du tabouret, le figuier remplit toute la vitre.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le volet. On a entendu toute ta phrase. Sa main a gardé la chaleur de la nappe. Du tabouret, le figuier remplit toute la vitre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le volet. Tes mots sont arrivés, cette fois. Sa main a gardé la chaleur de la nappe. Du tabouret, le figuier remplit toute la vitre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le volet. On a entendu toute ta phrase. Sa main a gardé la chaleur de la nappe. Du tabouret, le figuier remplit toute la vitre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné sur la table, avec le tabouret, puis le volet. Tes mots sont arrivés, cette fois. Sa main a gardé la chaleur de la nappe. Du tabouret, le figuier remplit toute la vitre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -12078,7 +12078,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné sur la table, avec le tabouret, puis le volet.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa main a gardé la chaleur de la nappe.
 narrateur|Du tabouret, le figuier remplit toute la vitre.</t>
         </is>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>L'ardoise fraîche veut le clou, près de la vitre. Aniss marche trop vite, l'éponge sous le bras. Je le mets ici, pile ! Maman cherche ses mots sur le loquet. Une goutte file vers le rebord. Aniss s'arrête, talons au sol. Le clou est à toi. Le triangle pâle se pend, un peu froid. Les feuilles tapent, contre le verre. Elles applaudissent, peut-être. L'éponge reste sur le rebord, en sentinelle. Sa main laisse un croissant d'eau sous le clou. On le verra, chaque fois qu'on ouvre.</t>
+          <t>L'ardoise fraîche veut le clou, près de la vitre. Aniss marche trop vite, l'éponge sous le bras. Je le mets ici, pile ! Maman cherche ses mots sur le loquet. Une goutte file vers le rebord. Aniss s'arrête, talons au sol. Le clou est à toi. Le triangle pâle se pend, un peu froid. Les feuilles tapent, contre le verre. Elles applaudissent, peut-être. L'éponge reste sur le rebord, comme une garde. Sa main laisse un croissant d'eau sous le clou. On le verra, chaque fois qu'on ouvre.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;L'ardoise fraîche veut le clou, près de la vitre. Aniss marche trop vite, l'éponge sous le bras. Je le mets ici, pile ! Maman cherche ses mots sur le loquet. Une goutte file vers le rebord. Aniss s'arrête, talons au sol. Le clou est à toi. Le triangle pâle se pend, un peu froid. Les feuilles tapent, contre le verre. Elles applaudissent, peut-être. L'éponge reste sur le rebord, en sentinelle. Sa main laisse un croissant d'eau sous le clou. On le verra, chaque fois qu'on ouvre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;L'ardoise fraîche veut le clou, près de la vitre. Aniss marche trop vite, l'éponge sous le bras. Je le mets ici, pile ! Maman cherche ses mots sur le loquet. Une goutte file vers le rebord. Aniss s'arrête, talons au sol. Le clou est à toi. Le triangle pâle se pend, un peu froid. Les feuilles tapent, contre le verre. Elles applaudissent, peut-être. L'éponge reste sur le rebord, comme une garde. Sa main laisse un croissant d'eau sous le clou. On le verra, chaque fois qu'on ouvre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>L'ardoise fraîche veut le clou, près de la vitre. Aniss marche trop vite, l'éponge sous le bras. Je le mets ici, pile ! Maman cherche ses mots sur le loquet. Une goutte file vers le rebord. Aniss s'arrête, talons au sol. Le clou est à toi. Le triangle pâle se pend, un peu froid. Les feuilles tapent, contre le verre. Elles applaudissent, peut-être. L'éponge reste sur le rebord, en sentinelle. Sa main laisse un croissant d'eau sous le clou. On le verra, chaque fois qu'on ouvre. [pause]</t>
+          <t>L'ardoise fraîche veut le clou, près de la vitre. Aniss marche trop vite, l'éponge sous le bras. Je le mets ici, pile ! Maman cherche ses mots sur le loquet. Une goutte file vers le rebord. Aniss s'arrête, talons au sol. Le clou est à toi. Le triangle pâle se pend, un peu froid. Les feuilles tapent, contre le verre. Elles applaudissent, peut-être. L'éponge reste sur le rebord, comme une garde. Sa main laisse un croissant d'eau sous le clou. On le verra, chaque fois qu'on ouvre. [pause]</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -13413,7 +13413,7 @@
 narrateur|Le triangle pâle se pend, un peu froid.
 enfant-m|Les feuilles tapent, contre le verre.
 papa|Elles applaudissent, peut-être.
-narrateur|L'éponge reste sur le rebord, en sentinelle.
+narrateur|L'éponge reste sur le rebord, comme une garde.
 narrateur|Sa main laisse un croissant d'eau sous le clou.
 maman|On le verra, chaque fois qu'on ouvre.</t>
         </is>
@@ -13447,17 +13447,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le clou. On a entendu toute ta phrase. Sa main sent le rebord, et un peu d'eau. Les feuilles du figuier tapent la vitre, contre l'ardoise.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le clou. Tes mots sont arrivés, cette fois. Sa main sent le rebord, et un peu d'eau. Les feuilles du figuier tapent la vitre, contre l'ardoise.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le clou. On a entendu toute ta phrase. Sa main sent le rebord, et un peu d'eau. Les feuilles du figuier tapent la vitre, contre l'ardoise.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le clou. Tes mots sont arrivés, cette fois. Sa main sent le rebord, et un peu d'eau. Les feuilles du figuier tapent la vitre, contre l'ardoise.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le clou. On a entendu toute ta phrase. Sa main sent le rebord, et un peu d'eau. Les feuilles du figuier tapent la vitre, contre l'ardoise.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le clou. Tes mots sont arrivés, cette fois. Sa main sent le rebord, et un peu d'eau. Les feuilles du figuier tapent la vitre, contre l'ardoise.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -13595,7 +13595,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné près de la fenêtre, avec l'éponge, puis le clou.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa main sent le rebord, et un peu d'eau.
 narrateur|Les feuilles du figuier tapent la vitre, contre l'ardoise.</t>
         </is>
@@ -13629,17 +13629,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Aniss apporte l'ardoise mouillée vers le pain, à la fenêtre. Le rebord est étroit. On mange avec lui ! Papa pose deux tasses, et compte à voix haute. L'ardoise glisse d'un souffle. Aniss la plaque, sans parler. Il attend la deuxième tasse. Voilà, c'est posé. Ton dessin peut s'asseoir. Il sèche au soleil du pain. On croque, et lui sèche. Une goutte meurt sur la croûte, minuscule. Sa main sent le tiède du rebord.</t>
+          <t>Aniss apporte l'ardoise mouillée vers le pain, à la fenêtre. Le rebord est étroit. On mange avec lui ! Papa pose deux tasses, et compte à voix haute. L'ardoise glisse d'un souffle. Aniss la retient, sans parler. Il attend la deuxième tasse. Voilà, c'est posé. Ton dessin peut s'asseoir. Il sèche au soleil du pain. On croque, et lui sèche. Une goutte meurt sur la croûte, minuscule. Sa main sent le tiède du rebord.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss apporte l'ardoise mouillée vers le pain, à la fenêtre. Le rebord est étroit. On mange avec lui ! Papa pose deux tasses, et compte à voix haute. L'ardoise glisse d'un souffle. Aniss la plaque, sans parler. Il attend la deuxième tasse. Voilà, c'est posé. Ton dessin peut s'asseoir. Il sèche au soleil du pain. On croque, et lui sèche. Une goutte meurt sur la croûte, minuscule. Sa main sent le tiède du rebord.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss apporte l'ardoise mouillée vers le pain, à la fenêtre. Le rebord est étroit. On mange avec lui ! Papa pose deux tasses, et compte à voix haute. L'ardoise glisse d'un souffle. Aniss la retient, sans parler. Il attend la deuxième tasse. Voilà, c'est posé. Ton dessin peut s'asseoir. Il sèche au soleil du pain. On croque, et lui sèche. Une goutte meurt sur la croûte, minuscule. Sa main sent le tiède du rebord.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Aniss apporte l'ardoise mouillée vers le pain, à la fenêtre. Le rebord est étroit. On mange avec lui ! Papa pose deux tasses, et compte à voix haute. L'ardoise glisse d'un souffle. Aniss la plaque, sans parler. Il attend la deuxième tasse. Voilà, c'est posé. Ton dessin peut s'asseoir. Il sèche au soleil du pain. On croque, et lui sèche. Une goutte meurt sur la croûte, minuscule. Sa main sent le tiède du rebord. [pause]</t>
+          <t>Aniss apporte l'ardoise mouillée vers le pain, à la fenêtre. Le rebord est étroit. On mange avec lui ! Papa pose deux tasses, et compte à voix haute. L'ardoise glisse d'un souffle. Aniss la retient, sans parler. Il attend la deuxième tasse. Voilà, c'est posé. Ton dessin peut s'asseoir. Il sèche au soleil du pain. On croque, et lui sèche. Une goutte meurt sur la croûte, minuscule. Sa main sent le tiède du rebord. [pause]</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -13778,7 +13778,7 @@
 enfant-m|On mange avec lui !
 narrateur|Papa pose deux tasses, et compte à voix haute.
 narrateur|L'ardoise glisse d'un souffle.
-narrateur|Aniss la plaque, sans parler.
+narrateur|Aniss la retient, sans parler.
 narrateur|Il attend la deuxième tasse.
 papa|Voilà, c'est posé.
 papa|Ton dessin peut s'asseoir.
@@ -13817,17 +13817,17 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le pain. On a entendu toute ta phrase. Sa main sent le rebord, et un peu d'eau. Ils croquent près de la fenêtre ; le dessin sèche.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le pain. Tes mots sont arrivés, cette fois. Sa main sent le rebord, et un peu d'eau. Ils croquent près de la fenêtre ; le dessin sèche.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le pain. On a entendu toute ta phrase. Sa main sent le rebord, et un peu d'eau. Ils croquent près de la fenêtre ; le dessin sèche.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le pain. Tes mots sont arrivés, cette fois. Sa main sent le rebord, et un peu d'eau. Ils croquent près de la fenêtre ; le dessin sèche.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le pain. On a entendu toute ta phrase. Sa main sent le rebord, et un peu d'eau. Ils croquent près de la fenêtre ; le dessin sèche.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le pain. Tes mots sont arrivés, cette fois. Sa main sent le rebord, et un peu d'eau. Ils croquent près de la fenêtre ; le dessin sèche.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -13965,7 +13965,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné près de la fenêtre, avec l'éponge, puis le pain.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa main sent le rebord, et un peu d'eau.
 narrateur|Ils croquent près de la fenêtre ; le dessin sèche.</t>
         </is>
@@ -14187,17 +14187,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le volet. On a entendu toute ta phrase. Sa main sent le rebord, et un peu d'eau. L'éponge et le volet sentent l'eau et le bois.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le volet. Tes mots sont arrivés, cette fois. Sa main sent le rebord, et un peu d'eau. L'éponge et le volet sentent l'eau et le bois.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le volet. On a entendu toute ta phrase. Sa main sent le rebord, et un peu d'eau. L'éponge et le volet sentent l'eau et le bois.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le volet. Tes mots sont arrivés, cette fois. Sa main sent le rebord, et un peu d'eau. L'éponge et le volet sentent l'eau et le bois.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le volet. On a entendu toute ta phrase. Sa main sent le rebord, et un peu d'eau. L'éponge et le volet sentent l'eau et le bois.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec l'éponge, puis le volet. Tes mots sont arrivés, cette fois. Sa main sent le rebord, et un peu d'eau. L'éponge et le volet sentent l'eau et le bois.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -14335,7 +14335,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné près de la fenêtre, avec l'éponge, puis le volet.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa main sent le rebord, et un peu d'eau.
 narrateur|L'éponge et le volet sentent l'eau et le bois.</t>
         </is>
@@ -14759,17 +14759,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>La craie jaune veut un dernier point, sous le clou. Aniss parle pendant que maman ouvre. Un soleil, juste là ! Le volet prend sa phrase. Le soleil devient une virgule. Aniss attend que le bois s'arrête. Recommence le soleil. Un rond jaune s'installe, propre. Il chauffe le cerf-volant du mur. Une virgule jaune reste sous le clou, en trop. Aniss la chasse d'un doigt. Sa main porte un petit astre. Le clou a son étoile.</t>
+          <t>La craie jaune veut un dernier point, sous le clou. Aniss parle pendant que maman ouvre. Un soleil, juste là ! Le volet prend sa phrase. Le soleil devient une virgule. Aniss attend que le bois s'arrête. Recommence le soleil. Un rond jaune s'installe, propre. Il chauffe le cerf-volant du mur. Une virgule jaune reste sous le clou, en trop. Aniss la chasse d'un doigt. Sa main porte un petit soleil. Le clou a son étoile.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La craie jaune veut un dernier point, sous le clou. Aniss parle pendant que maman ouvre. Un soleil, juste là ! Le volet prend sa phrase. Le soleil devient une virgule. Aniss attend que le bois s'arrête. Recommence le soleil. Un rond jaune s'installe, propre. Il chauffe le cerf-volant du mur. Une virgule jaune reste sous le clou, en trop. Aniss la chasse d'un doigt. Sa main porte un petit astre. Le clou a son étoile.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La craie jaune veut un dernier point, sous le clou. Aniss parle pendant que maman ouvre. Un soleil, juste là ! Le volet prend sa phrase. Le soleil devient une virgule. Aniss attend que le bois s'arrête. Recommence le soleil. Un rond jaune s'installe, propre. Il chauffe le cerf-volant du mur. Une virgule jaune reste sous le clou, en trop. Aniss la chasse d'un doigt. Sa main porte un petit soleil. Le clou a son étoile.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>La craie jaune veut un dernier point, sous le clou. Aniss parle pendant que maman ouvre. Un soleil, juste là ! Le volet prend sa phrase. Le soleil devient une virgule. Aniss attend que le bois s'arrête. Recommence le soleil. Un rond jaune s'installe, propre. Il chauffe le cerf-volant du mur. Une virgule jaune reste sous le clou, en trop. Aniss la chasse d'un doigt. Sa main porte un petit astre. Le clou a son étoile. [pause]</t>
+          <t>La craie jaune veut un dernier point, sous le clou. Aniss parle pendant que maman ouvre. Un soleil, juste là ! Le volet prend sa phrase. Le soleil devient une virgule. Aniss attend que le bois s'arrête. Recommence le soleil. Un rond jaune s'installe, propre. Il chauffe le cerf-volant du mur. Une virgule jaune reste sous le clou, en trop. Aniss la chasse d'un doigt. Sa main porte un petit soleil. Le clou a son étoile. [pause]</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -14914,7 +14914,7 @@
 enfant-m|Il chauffe le cerf-volant du mur.
 papa|Une virgule jaune reste sous le clou, en trop.
 narrateur|Aniss la chasse d'un doigt.
-narrateur|Sa main porte un petit astre.
+narrateur|Sa main porte un petit soleil.
 maman|Le clou a son étoile.</t>
         </is>
       </c>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le clou. On a entendu toute ta phrase. Un grain de craie lui tient lieu d'anneau. Une virgule jaune de craie reste sous le clou.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le clou. Tes mots sont arrivés, cette fois. Un grain de craie lui tient lieu d'anneau. Une virgule jaune de craie reste sous le clou.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le clou. On a entendu toute ta phrase. Un grain de craie lui tient lieu d'anneau. Une virgule jaune de craie reste sous le clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le clou. Tes mots sont arrivés, cette fois. Un grain de craie lui tient lieu d'anneau. Une virgule jaune de craie reste sous le clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le clou. On a entendu toute ta phrase. Un grain de craie lui tient lieu d'anneau. Une virgule jaune de craie reste sous le clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le clou. Tes mots sont arrivés, cette fois. Un grain de craie lui tient lieu d'anneau. Une virgule jaune de craie reste sous le clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -15095,7 +15095,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné près de la fenêtre, avec la craie neuve, puis le clou.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Un grain de craie lui tient lieu d'anneau.
 narrateur|Une virgule jaune de craie reste sous le clou.</t>
         </is>
@@ -15317,17 +15317,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le pain. On a entendu toute ta phrase. Un grain de craie lui tient lieu d'anneau. Derrière le pain, le vrai cerf-volant rouge salue la vitre.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le pain. Tes mots sont arrivés, cette fois. Un grain de craie lui tient lieu d'anneau. Derrière le pain, le vrai cerf-volant rouge salue la vitre.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le pain. On a entendu toute ta phrase. Un grain de craie lui tient lieu d'anneau. Derrière le pain, le vrai cerf-volant rouge salue la vitre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le pain. Tes mots sont arrivés, cette fois. Un grain de craie lui tient lieu d'anneau. Derrière le pain, le vrai cerf-volant rouge salue la vitre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le pain. On a entendu toute ta phrase. Un grain de craie lui tient lieu d'anneau. Derrière le pain, le vrai cerf-volant rouge salue la vitre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le pain. Tes mots sont arrivés, cette fois. Un grain de craie lui tient lieu d'anneau. Derrière le pain, le vrai cerf-volant rouge salue la vitre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -15465,7 +15465,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné près de la fenêtre, avec la craie neuve, puis le pain.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Un grain de craie lui tient lieu d'anneau.
 narrateur|Derrière le pain, le vrai cerf-volant rouge salue la vitre.</t>
         </is>
@@ -15687,17 +15687,17 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le volet. On a entendu toute ta phrase. Un grain de craie lui tient lieu d'anneau. Deux cerfs-volants se regardent : l'un rouge, l'un blanc.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le volet. Tes mots sont arrivés, cette fois. Un grain de craie lui tient lieu d'anneau. Deux cerfs-volants se regardent : l'un rouge, l'un blanc.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le volet. On a entendu toute ta phrase. Un grain de craie lui tient lieu d'anneau. Deux cerfs-volants se regardent : l'un rouge, l'un blanc.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le volet. Tes mots sont arrivés, cette fois. Un grain de craie lui tient lieu d'anneau. Deux cerfs-volants se regardent : l'un rouge, l'un blanc.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le volet. On a entendu toute ta phrase. Un grain de craie lui tient lieu d'anneau. Deux cerfs-volants se regardent : l'un rouge, l'un blanc.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec la craie neuve, puis le volet. Tes mots sont arrivés, cette fois. Un grain de craie lui tient lieu d'anneau. Deux cerfs-volants se regardent : l'un rouge, l'un blanc.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -15835,7 +15835,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné près de la fenêtre, avec la craie neuve, puis le volet.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Un grain de craie lui tient lieu d'anneau.
 narrateur|Deux cerfs-volants se regardent : l'un rouge, l'un blanc.</t>
         </is>
@@ -16447,17 +16447,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le clou. On a entendu toute ta phrase. Sa main quitte le loquet, sans se presser. Aniss accroche l'ardoise sans redescendre du tabouret.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le clou. Tes mots sont arrivés, cette fois. Sa main quitte le loquet, sans se presser. Aniss accroche l'ardoise sans redescendre du tabouret.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le clou. On a entendu toute ta phrase. Sa main quitte le loquet, sans se presser. Aniss accroche l'ardoise sans redescendre du tabouret.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le clou. Tes mots sont arrivés, cette fois. Sa main quitte le loquet, sans se presser. Aniss accroche l'ardoise sans redescendre du tabouret.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le clou. On a entendu toute ta phrase. Sa main quitte le loquet, sans se presser. Aniss accroche l'ardoise sans redescendre du tabouret.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le clou. Tes mots sont arrivés, cette fois. Sa main quitte le loquet, sans se presser. Aniss accroche l'ardoise sans redescendre du tabouret.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -16595,7 +16595,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné près de la fenêtre, avec le tabouret, puis le clou.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa main quitte le loquet, sans se presser.
 narrateur|Aniss accroche l'ardoise sans redescendre du tabouret.</t>
         </is>
@@ -16817,17 +16817,17 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le pain. On a entendu toute ta phrase. Sa main quitte le loquet, sans se presser. Le pain reste sur le rebord, l'ardoise sur ses genoux.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le pain. Tes mots sont arrivés, cette fois. Sa main quitte le loquet, sans se presser. Le pain reste sur le rebord, l'ardoise sur ses genoux.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le pain. On a entendu toute ta phrase. Sa main quitte le loquet, sans se presser. Le pain reste sur le rebord, l'ardoise sur ses genoux.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le pain. Tes mots sont arrivés, cette fois. Sa main quitte le loquet, sans se presser. Le pain reste sur le rebord, l'ardoise sur ses genoux.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le pain. On a entendu toute ta phrase. Sa main quitte le loquet, sans se presser. Le pain reste sur le rebord, l'ardoise sur ses genoux.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le pain. Tes mots sont arrivés, cette fois. Sa main quitte le loquet, sans se presser. Le pain reste sur le rebord, l'ardoise sur ses genoux.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -16965,7 +16965,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné près de la fenêtre, avec le tabouret, puis le pain.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa main quitte le loquet, sans se presser.
 narrateur|Le pain reste sur le rebord, l'ardoise sur ses genoux.</t>
         </is>
@@ -16999,17 +16999,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Aniss, tabouret et volet, veut tenir trois choses. L'ardoise, le loquet, et sa phrase. Regardez les trois ! Le vent, papa, et lui parlent ensemble. Rien n'est clair. Aniss choisit le silence, une seconde. On se tait. Montre. Le tabouret, le volet, et ma main. Trois choses sages, et un cerf-volant. Le bois, le bois, et la peau se tiennent. Dehors, le rouge reste, pour un peu. Sa main, au loquet, ne serre plus trop.</t>
+          <t>Aniss, tabouret et volet, veut tenir trois choses. L'ardoise, le loquet, et sa phrase. Regardez les trois ! Le vent, papa, et lui parlent ensemble. Rien n'est clair. Aniss choisit le silence, une seconde. On se tait. Montre. Le tabouret, le volet, et ma main. Trois choses sages, et un cerf-volant. Tabouret, volet, et main restent collés. Dehors, le rouge reste, pour un peu. Sa main, au loquet, ne serre plus trop.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss, tabouret et volet, veut tenir trois choses. L'ardoise, le loquet, et sa phrase. Regardez les trois ! Le vent, papa, et lui parlent ensemble. Rien n'est clair. Aniss choisit le silence, une seconde. On se tait. Montre. Le tabouret, le volet, et ma main. Trois choses sages, et un cerf-volant. Le bois, le bois, et la peau se tiennent. Dehors, le rouge reste, pour un peu. Sa main, au loquet, ne serre plus trop.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aniss, tabouret et volet, veut tenir trois choses. L'ardoise, le loquet, et sa phrase. Regardez les trois ! Le vent, papa, et lui parlent ensemble. Rien n'est clair. Aniss choisit le silence, une seconde. On se tait. Montre. Le tabouret, le volet, et ma main. Trois choses sages, et un cerf-volant. Tabouret, volet, et main restent collés. Dehors, le rouge reste, pour un peu. Sa main, au loquet, ne serre plus trop.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Aniss, tabouret et volet, veut tenir trois choses. L'ardoise, le loquet, et sa phrase. Regardez les trois ! Le vent, papa, et lui parlent ensemble. Rien n'est clair. Aniss choisit le silence, une seconde. On se tait. Montre. Le tabouret, le volet, et ma main. Trois choses sages, et un cerf-volant. Le bois, le bois, et la peau se tiennent. Dehors, le rouge reste, pour un peu. Sa main, au loquet, ne serre plus trop. [pause]</t>
+          <t>Aniss, tabouret et volet, veut tenir trois choses. L'ardoise, le loquet, et sa phrase. Regardez les trois ! Le vent, papa, et lui parlent ensemble. Rien n'est clair. Aniss choisit le silence, une seconde. On se tait. Montre. Le tabouret, le volet, et ma main. Trois choses sages, et un cerf-volant. Tabouret, volet, et main restent collés. Dehors, le rouge reste, pour un peu. Sa main, au loquet, ne serre plus trop. [pause]</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -17153,7 +17153,7 @@
 papa|Montre.
 enfant-m|Le tabouret, le volet, et ma main.
 maman|Trois choses sages, et un cerf-volant.
-narrateur|Le bois, le bois, et la peau se tiennent.
+narrateur|Tabouret, volet, et main restent collés.
 narrateur|Dehors, le rouge reste, pour un peu.
 narrateur|Sa main, au loquet, ne serre plus trop.</t>
         </is>
@@ -17187,17 +17187,17 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le volet. On a entendu toute ta phrase. Sa main quitte le loquet, sans se presser. Le tabouret, le volet, et sa main restent tranquilles.</t>
+          <t>Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le volet. Tes mots sont arrivés, cette fois. Sa main quitte le loquet, sans se presser. Le tabouret, le volet, et sa main restent tranquilles.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le volet. On a entendu toute ta phrase. Sa main quitte le loquet, sans se presser. Le tabouret, le volet, et sa main restent tranquilles.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le volet. Tes mots sont arrivés, cette fois. Sa main quitte le loquet, sans se presser. Le tabouret, le volet, et sa main restent tranquilles.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le volet. On a entendu toute ta phrase. Sa main quitte le loquet, sans se presser. Le tabouret, le volet, et sa main restent tranquilles.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, et le soleil baisse. À toi, Aniss. Nous t'écoutons jusqu'au bout. J'ai dessiné près de la fenêtre, avec le tabouret, puis le volet. Tes mots sont arrivés, cette fois. Sa main quitte le loquet, sans se presser. Le tabouret, le volet, et sa main restent tranquilles.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -17335,7 +17335,7 @@
 papa|À toi, Aniss.
 papa|Nous t'écoutons jusqu'au bout.
 enfant-m|J'ai dessiné près de la fenêtre, avec le tabouret, puis le volet.
-maman|On a entendu toute ta phrase.
+maman|Tes mots sont arrivés, cette fois.
 narrateur|Sa main quitte le loquet, sans se presser.
 narrateur|Le tabouret, le volet, et sa main restent tranquilles.</t>
         </is>
@@ -17363,7 +17363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17476,6 +17476,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
